--- a/output/version3/test/20-10/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C2" t="n">
-        <v>912</v>
+        <v>851</v>
       </c>
       <c r="D2" t="n">
-        <v>1005</v>
+        <v>991</v>
       </c>
       <c r="E2" t="n">
-        <v>965</v>
+        <v>870</v>
       </c>
       <c r="F2" t="n">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="G2" t="n">
-        <v>879</v>
+        <v>1021</v>
       </c>
       <c r="H2" t="n">
-        <v>850</v>
+        <v>977</v>
       </c>
       <c r="I2" t="n">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="J2" t="n">
-        <v>957</v>
+        <v>838</v>
       </c>
       <c r="K2" t="n">
-        <v>875</v>
+        <v>948</v>
       </c>
       <c r="L2" t="n">
-        <v>901.9</v>
+        <v>911</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>859</v>
+        <v>977</v>
       </c>
       <c r="C3" t="n">
-        <v>864</v>
+        <v>836</v>
       </c>
       <c r="D3" t="n">
-        <v>911</v>
+        <v>847</v>
       </c>
       <c r="E3" t="n">
+        <v>962</v>
+      </c>
+      <c r="F3" t="n">
+        <v>995</v>
+      </c>
+      <c r="G3" t="n">
+        <v>917</v>
+      </c>
+      <c r="H3" t="n">
+        <v>931</v>
+      </c>
+      <c r="I3" t="n">
+        <v>894</v>
+      </c>
+      <c r="J3" t="n">
+        <v>942</v>
+      </c>
+      <c r="K3" t="n">
         <v>966</v>
       </c>
-      <c r="F3" t="n">
-        <v>895</v>
-      </c>
-      <c r="G3" t="n">
-        <v>921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>894</v>
-      </c>
-      <c r="I3" t="n">
-        <v>889</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1026</v>
-      </c>
-      <c r="K3" t="n">
-        <v>890</v>
-      </c>
       <c r="L3" t="n">
-        <v>911.5</v>
+        <v>926.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>843</v>
+        <v>963</v>
       </c>
       <c r="C4" t="n">
-        <v>967</v>
+        <v>801</v>
       </c>
       <c r="D4" t="n">
-        <v>825</v>
+        <v>902</v>
       </c>
       <c r="E4" t="n">
-        <v>967</v>
+        <v>799</v>
       </c>
       <c r="F4" t="n">
-        <v>803</v>
+        <v>903</v>
       </c>
       <c r="G4" t="n">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="H4" t="n">
-        <v>899</v>
+        <v>856</v>
       </c>
       <c r="I4" t="n">
-        <v>874</v>
+        <v>1027</v>
       </c>
       <c r="J4" t="n">
-        <v>863</v>
+        <v>926</v>
       </c>
       <c r="K4" t="n">
-        <v>869</v>
+        <v>942</v>
       </c>
       <c r="L4" t="n">
-        <v>880.4</v>
+        <v>901.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>837</v>
+        <v>974</v>
       </c>
       <c r="C5" t="n">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="D5" t="n">
-        <v>851</v>
+        <v>917</v>
       </c>
       <c r="E5" t="n">
+        <v>727</v>
+      </c>
+      <c r="F5" t="n">
+        <v>815</v>
+      </c>
+      <c r="G5" t="n">
+        <v>864</v>
+      </c>
+      <c r="H5" t="n">
+        <v>884</v>
+      </c>
+      <c r="I5" t="n">
+        <v>903</v>
+      </c>
+      <c r="J5" t="n">
+        <v>866</v>
+      </c>
+      <c r="K5" t="n">
         <v>856</v>
       </c>
-      <c r="F5" t="n">
-        <v>869</v>
-      </c>
-      <c r="G5" t="n">
-        <v>802</v>
-      </c>
-      <c r="H5" t="n">
-        <v>845</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1005</v>
-      </c>
-      <c r="J5" t="n">
-        <v>966</v>
-      </c>
-      <c r="K5" t="n">
-        <v>760</v>
-      </c>
       <c r="L5" t="n">
-        <v>867.6</v>
+        <v>867.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>876</v>
+        <v>803</v>
       </c>
       <c r="C6" t="n">
-        <v>884</v>
+        <v>941</v>
       </c>
       <c r="D6" t="n">
-        <v>1020</v>
+        <v>828</v>
       </c>
       <c r="E6" t="n">
-        <v>996</v>
+        <v>843</v>
       </c>
       <c r="F6" t="n">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="G6" t="n">
-        <v>1006</v>
+        <v>914</v>
       </c>
       <c r="H6" t="n">
-        <v>824</v>
+        <v>848</v>
       </c>
       <c r="I6" t="n">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="J6" t="n">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="K6" t="n">
-        <v>845</v>
+        <v>940</v>
       </c>
       <c r="L6" t="n">
-        <v>908.9</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>800</v>
+        <v>858</v>
       </c>
       <c r="C7" t="n">
-        <v>813</v>
+        <v>880</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="E7" t="n">
-        <v>1022</v>
+        <v>844</v>
       </c>
       <c r="F7" t="n">
-        <v>867</v>
+        <v>910</v>
       </c>
       <c r="G7" t="n">
-        <v>917</v>
+        <v>870</v>
       </c>
       <c r="H7" t="n">
-        <v>818</v>
+        <v>918</v>
       </c>
       <c r="I7" t="n">
-        <v>1062</v>
+        <v>812</v>
       </c>
       <c r="J7" t="n">
-        <v>868</v>
+        <v>806</v>
       </c>
       <c r="K7" t="n">
-        <v>830</v>
+        <v>941</v>
       </c>
       <c r="L7" t="n">
-        <v>883.5</v>
+        <v>865.8</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>977</v>
+        <v>1024</v>
       </c>
       <c r="C8" t="n">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="D8" t="n">
-        <v>912</v>
+        <v>857</v>
       </c>
       <c r="E8" t="n">
-        <v>879</v>
+        <v>901</v>
       </c>
       <c r="F8" t="n">
-        <v>820</v>
+        <v>891</v>
       </c>
       <c r="G8" t="n">
-        <v>842</v>
+        <v>789</v>
       </c>
       <c r="H8" t="n">
-        <v>848</v>
+        <v>926</v>
       </c>
       <c r="I8" t="n">
-        <v>776</v>
+        <v>900</v>
       </c>
       <c r="J8" t="n">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="K8" t="n">
-        <v>775</v>
+        <v>953</v>
       </c>
       <c r="L8" t="n">
-        <v>855.9</v>
+        <v>905.5</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>932</v>
+        <v>987</v>
       </c>
       <c r="C9" t="n">
+        <v>911</v>
+      </c>
+      <c r="D9" t="n">
+        <v>850</v>
+      </c>
+      <c r="E9" t="n">
+        <v>853</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1061</v>
+      </c>
+      <c r="G9" t="n">
+        <v>928</v>
+      </c>
+      <c r="H9" t="n">
+        <v>930</v>
+      </c>
+      <c r="I9" t="n">
+        <v>957</v>
+      </c>
+      <c r="J9" t="n">
         <v>983</v>
       </c>
-      <c r="D9" t="n">
-        <v>872</v>
-      </c>
-      <c r="E9" t="n">
-        <v>910</v>
-      </c>
-      <c r="F9" t="n">
-        <v>964</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1040</v>
-      </c>
-      <c r="H9" t="n">
-        <v>906</v>
-      </c>
-      <c r="I9" t="n">
-        <v>919</v>
-      </c>
-      <c r="J9" t="n">
-        <v>848</v>
-      </c>
       <c r="K9" t="n">
-        <v>941</v>
+        <v>951</v>
       </c>
       <c r="L9" t="n">
-        <v>931.5</v>
+        <v>941.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C10" t="n">
-        <v>767</v>
+        <v>732</v>
       </c>
       <c r="D10" t="n">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E10" t="n">
-        <v>859</v>
+        <v>911</v>
       </c>
       <c r="F10" t="n">
-        <v>884</v>
+        <v>761</v>
       </c>
       <c r="G10" t="n">
-        <v>813</v>
+        <v>864</v>
       </c>
       <c r="H10" t="n">
-        <v>858</v>
+        <v>939</v>
       </c>
       <c r="I10" t="n">
-        <v>914</v>
+        <v>792</v>
       </c>
       <c r="J10" t="n">
-        <v>963</v>
+        <v>773</v>
       </c>
       <c r="K10" t="n">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L10" t="n">
-        <v>859.8</v>
+        <v>831.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>945</v>
+        <v>905</v>
       </c>
       <c r="C11" t="n">
-        <v>773</v>
+        <v>739</v>
       </c>
       <c r="D11" t="n">
-        <v>888</v>
+        <v>770</v>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="F11" t="n">
-        <v>822</v>
+        <v>896</v>
       </c>
       <c r="G11" t="n">
-        <v>912</v>
+        <v>782</v>
       </c>
       <c r="H11" t="n">
-        <v>813</v>
+        <v>892</v>
       </c>
       <c r="I11" t="n">
-        <v>905</v>
+        <v>771</v>
       </c>
       <c r="J11" t="n">
-        <v>795</v>
+        <v>923</v>
       </c>
       <c r="K11" t="n">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="L11" t="n">
-        <v>842.2</v>
+        <v>831.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="C12" t="n">
-        <v>851</v>
+        <v>784</v>
       </c>
       <c r="D12" t="n">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="E12" t="n">
-        <v>856</v>
+        <v>784</v>
       </c>
       <c r="F12" t="n">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="G12" t="n">
-        <v>845</v>
+        <v>817</v>
       </c>
       <c r="H12" t="n">
-        <v>796</v>
+        <v>909</v>
       </c>
       <c r="I12" t="n">
-        <v>783</v>
+        <v>917</v>
       </c>
       <c r="J12" t="n">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="K12" t="n">
-        <v>899</v>
+        <v>833</v>
       </c>
       <c r="L12" t="n">
-        <v>846.2</v>
+        <v>846.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>877</v>
+        <v>928</v>
       </c>
       <c r="C13" t="n">
-        <v>879</v>
+        <v>972</v>
       </c>
       <c r="D13" t="n">
-        <v>997</v>
+        <v>1025</v>
       </c>
       <c r="E13" t="n">
-        <v>862</v>
+        <v>902</v>
       </c>
       <c r="F13" t="n">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G13" t="n">
-        <v>741</v>
+        <v>878</v>
       </c>
       <c r="H13" t="n">
-        <v>788</v>
+        <v>855</v>
       </c>
       <c r="I13" t="n">
-        <v>835</v>
+        <v>957</v>
       </c>
       <c r="J13" t="n">
-        <v>943</v>
+        <v>972</v>
       </c>
       <c r="K13" t="n">
-        <v>985</v>
+        <v>850</v>
       </c>
       <c r="L13" t="n">
-        <v>881.9</v>
+        <v>925</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>914</v>
+        <v>848</v>
       </c>
       <c r="C14" t="n">
-        <v>924</v>
+        <v>991</v>
       </c>
       <c r="D14" t="n">
-        <v>920</v>
+        <v>831</v>
       </c>
       <c r="E14" t="n">
-        <v>911</v>
+        <v>840</v>
       </c>
       <c r="F14" t="n">
-        <v>1011</v>
+        <v>980</v>
       </c>
       <c r="G14" t="n">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="H14" t="n">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="I14" t="n">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="J14" t="n">
-        <v>908</v>
+        <v>950</v>
       </c>
       <c r="K14" t="n">
-        <v>923</v>
+        <v>975</v>
       </c>
       <c r="L14" t="n">
-        <v>921</v>
+        <v>911.9</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>947</v>
+        <v>930</v>
       </c>
       <c r="C15" t="n">
-        <v>959</v>
+        <v>906</v>
       </c>
       <c r="D15" t="n">
-        <v>966</v>
+        <v>820</v>
       </c>
       <c r="E15" t="n">
-        <v>923</v>
+        <v>940</v>
       </c>
       <c r="F15" t="n">
-        <v>885</v>
+        <v>828</v>
       </c>
       <c r="G15" t="n">
-        <v>905</v>
+        <v>988</v>
       </c>
       <c r="H15" t="n">
-        <v>1033</v>
+        <v>919</v>
       </c>
       <c r="I15" t="n">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="J15" t="n">
-        <v>937</v>
+        <v>965</v>
       </c>
       <c r="K15" t="n">
-        <v>992</v>
+        <v>880</v>
       </c>
       <c r="L15" t="n">
-        <v>959.1</v>
+        <v>923.1</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C16" t="n">
-        <v>937</v>
+        <v>810</v>
       </c>
       <c r="D16" t="n">
-        <v>846</v>
+        <v>944</v>
       </c>
       <c r="E16" t="n">
-        <v>880</v>
+        <v>807</v>
       </c>
       <c r="F16" t="n">
-        <v>843</v>
+        <v>933</v>
       </c>
       <c r="G16" t="n">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="H16" t="n">
-        <v>825</v>
+        <v>859</v>
       </c>
       <c r="I16" t="n">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="J16" t="n">
-        <v>844</v>
+        <v>903</v>
       </c>
       <c r="K16" t="n">
-        <v>932</v>
+        <v>797</v>
       </c>
       <c r="L16" t="n">
-        <v>863.2</v>
+        <v>863.1</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="C17" t="n">
-        <v>825</v>
+        <v>763</v>
       </c>
       <c r="D17" t="n">
-        <v>871</v>
+        <v>799</v>
       </c>
       <c r="E17" t="n">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="F17" t="n">
-        <v>842</v>
+        <v>734</v>
       </c>
       <c r="G17" t="n">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H17" t="n">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="I17" t="n">
-        <v>831</v>
+        <v>744</v>
       </c>
       <c r="J17" t="n">
-        <v>865</v>
+        <v>798</v>
       </c>
       <c r="K17" t="n">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="L17" t="n">
-        <v>813</v>
+        <v>783.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="C18" t="n">
-        <v>921</v>
+        <v>951</v>
       </c>
       <c r="D18" t="n">
-        <v>1055</v>
+        <v>875</v>
       </c>
       <c r="E18" t="n">
-        <v>1086</v>
+        <v>981</v>
       </c>
       <c r="F18" t="n">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="G18" t="n">
-        <v>1040</v>
+        <v>907</v>
       </c>
       <c r="H18" t="n">
-        <v>1058</v>
+        <v>842</v>
       </c>
       <c r="I18" t="n">
-        <v>895</v>
+        <v>1139</v>
       </c>
       <c r="J18" t="n">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="K18" t="n">
-        <v>1026</v>
+        <v>943</v>
       </c>
       <c r="L18" t="n">
-        <v>1004.2</v>
+        <v>960.3</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>875</v>
+        <v>731</v>
       </c>
       <c r="C19" t="n">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D19" t="n">
-        <v>885</v>
+        <v>744</v>
       </c>
       <c r="E19" t="n">
-        <v>804</v>
+        <v>719</v>
       </c>
       <c r="F19" t="n">
-        <v>799</v>
+        <v>751</v>
       </c>
       <c r="G19" t="n">
-        <v>764</v>
+        <v>722</v>
       </c>
       <c r="H19" t="n">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="I19" t="n">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="J19" t="n">
-        <v>792</v>
+        <v>859</v>
       </c>
       <c r="K19" t="n">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="L19" t="n">
-        <v>807.4</v>
+        <v>764.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>920</v>
+        <v>785</v>
       </c>
       <c r="C20" t="n">
-        <v>787</v>
+        <v>750</v>
       </c>
       <c r="D20" t="n">
-        <v>722</v>
+        <v>748</v>
       </c>
       <c r="E20" t="n">
-        <v>762</v>
+        <v>913</v>
       </c>
       <c r="F20" t="n">
-        <v>837</v>
+        <v>719</v>
       </c>
       <c r="G20" t="n">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="H20" t="n">
-        <v>796</v>
+        <v>820</v>
       </c>
       <c r="I20" t="n">
-        <v>830</v>
+        <v>900</v>
       </c>
       <c r="J20" t="n">
         <v>829</v>
       </c>
       <c r="K20" t="n">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="L20" t="n">
-        <v>814.4</v>
+        <v>810.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>815</v>
+        <v>882</v>
       </c>
       <c r="C21" t="n">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="D21" t="n">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="E21" t="n">
-        <v>834</v>
+        <v>892</v>
       </c>
       <c r="F21" t="n">
-        <v>960</v>
+        <v>856</v>
       </c>
       <c r="G21" t="n">
-        <v>889</v>
+        <v>859</v>
       </c>
       <c r="H21" t="n">
-        <v>942</v>
+        <v>802</v>
       </c>
       <c r="I21" t="n">
-        <v>887</v>
+        <v>978</v>
       </c>
       <c r="J21" t="n">
-        <v>863</v>
+        <v>941</v>
       </c>
       <c r="K21" t="n">
-        <v>1085</v>
+        <v>974</v>
       </c>
       <c r="L21" t="n">
-        <v>923.3</v>
+        <v>916.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>966</v>
+        <v>905</v>
       </c>
       <c r="C22" t="n">
-        <v>921</v>
+        <v>847</v>
       </c>
       <c r="D22" t="n">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="E22" t="n">
-        <v>884</v>
+        <v>771</v>
       </c>
       <c r="F22" t="n">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="G22" t="n">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="H22" t="n">
-        <v>826</v>
+        <v>843</v>
       </c>
       <c r="I22" t="n">
-        <v>765</v>
+        <v>932</v>
       </c>
       <c r="J22" t="n">
-        <v>1012</v>
+        <v>970</v>
       </c>
       <c r="K22" t="n">
-        <v>811</v>
+        <v>902</v>
       </c>
       <c r="L22" t="n">
-        <v>883.3</v>
+        <v>881.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>999</v>
+        <v>960</v>
       </c>
       <c r="C23" t="n">
-        <v>1047</v>
+        <v>934</v>
       </c>
       <c r="D23" t="n">
-        <v>876</v>
+        <v>948</v>
       </c>
       <c r="E23" t="n">
-        <v>1023</v>
+        <v>945</v>
       </c>
       <c r="F23" t="n">
-        <v>931</v>
+        <v>990</v>
       </c>
       <c r="G23" t="n">
-        <v>980</v>
+        <v>961</v>
       </c>
       <c r="H23" t="n">
-        <v>1013</v>
+        <v>816</v>
       </c>
       <c r="I23" t="n">
-        <v>894</v>
+        <v>1065</v>
       </c>
       <c r="J23" t="n">
-        <v>907</v>
+        <v>1037</v>
       </c>
       <c r="K23" t="n">
-        <v>882</v>
+        <v>1036</v>
       </c>
       <c r="L23" t="n">
-        <v>955.2</v>
+        <v>969.2</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>892</v>
+        <v>796</v>
       </c>
       <c r="C24" t="n">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="D24" t="n">
-        <v>919</v>
+        <v>873</v>
       </c>
       <c r="E24" t="n">
-        <v>825</v>
+        <v>801</v>
       </c>
       <c r="F24" t="n">
-        <v>759</v>
+        <v>824</v>
       </c>
       <c r="G24" t="n">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="H24" t="n">
-        <v>761</v>
+        <v>861</v>
       </c>
       <c r="I24" t="n">
-        <v>895</v>
+        <v>960</v>
       </c>
       <c r="J24" t="n">
-        <v>846</v>
+        <v>793</v>
       </c>
       <c r="K24" t="n">
-        <v>911</v>
+        <v>842</v>
       </c>
       <c r="L24" t="n">
-        <v>852.7</v>
+        <v>846.7</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>910</v>
+        <v>871</v>
       </c>
       <c r="C25" t="n">
-        <v>808</v>
+        <v>915</v>
       </c>
       <c r="D25" t="n">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="E25" t="n">
-        <v>868</v>
+        <v>882</v>
       </c>
       <c r="F25" t="n">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="G25" t="n">
-        <v>885</v>
+        <v>944</v>
       </c>
       <c r="H25" t="n">
-        <v>1118</v>
+        <v>833</v>
       </c>
       <c r="I25" t="n">
-        <v>865</v>
+        <v>942</v>
       </c>
       <c r="J25" t="n">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="K25" t="n">
-        <v>929</v>
+        <v>882</v>
       </c>
       <c r="L25" t="n">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1114</v>
+        <v>900</v>
       </c>
       <c r="C26" t="n">
-        <v>924</v>
+        <v>1025</v>
       </c>
       <c r="D26" t="n">
-        <v>940</v>
+        <v>998</v>
       </c>
       <c r="E26" t="n">
-        <v>889</v>
+        <v>999</v>
       </c>
       <c r="F26" t="n">
-        <v>1036</v>
+        <v>948</v>
       </c>
       <c r="G26" t="n">
-        <v>926</v>
+        <v>1017</v>
       </c>
       <c r="H26" t="n">
-        <v>1019</v>
+        <v>931</v>
       </c>
       <c r="I26" t="n">
         <v>1015</v>
       </c>
       <c r="J26" t="n">
-        <v>850</v>
+        <v>1016</v>
       </c>
       <c r="K26" t="n">
-        <v>873</v>
+        <v>1063</v>
       </c>
       <c r="L26" t="n">
-        <v>958.6</v>
+        <v>991.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1009</v>
+        <v>1051</v>
       </c>
       <c r="C27" t="n">
-        <v>1049</v>
+        <v>950</v>
       </c>
       <c r="D27" t="n">
-        <v>973</v>
+        <v>902</v>
       </c>
       <c r="E27" t="n">
-        <v>983</v>
+        <v>1089</v>
       </c>
       <c r="F27" t="n">
-        <v>887</v>
+        <v>976</v>
       </c>
       <c r="G27" t="n">
-        <v>1023</v>
+        <v>941</v>
       </c>
       <c r="H27" t="n">
-        <v>1006</v>
+        <v>1057</v>
       </c>
       <c r="I27" t="n">
-        <v>1071</v>
+        <v>1100</v>
       </c>
       <c r="J27" t="n">
-        <v>1067</v>
+        <v>1042</v>
       </c>
       <c r="K27" t="n">
-        <v>1040</v>
+        <v>981</v>
       </c>
       <c r="L27" t="n">
-        <v>1010.8</v>
+        <v>1008.9</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="C28" t="n">
-        <v>692</v>
+        <v>788</v>
       </c>
       <c r="D28" t="n">
-        <v>809</v>
+        <v>708</v>
       </c>
       <c r="E28" t="n">
-        <v>753</v>
+        <v>814</v>
       </c>
       <c r="F28" t="n">
-        <v>794</v>
+        <v>762</v>
       </c>
       <c r="G28" t="n">
-        <v>829</v>
+        <v>778</v>
       </c>
       <c r="H28" t="n">
-        <v>780</v>
+        <v>862</v>
       </c>
       <c r="I28" t="n">
-        <v>759</v>
+        <v>859</v>
       </c>
       <c r="J28" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="K28" t="n">
-        <v>739</v>
+        <v>871</v>
       </c>
       <c r="L28" t="n">
-        <v>784</v>
+        <v>814.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>921</v>
+        <v>874</v>
       </c>
       <c r="C29" t="n">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="D29" t="n">
-        <v>851</v>
+        <v>796</v>
       </c>
       <c r="E29" t="n">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="F29" t="n">
-        <v>919</v>
+        <v>836</v>
       </c>
       <c r="G29" t="n">
-        <v>1047</v>
+        <v>817</v>
       </c>
       <c r="H29" t="n">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="I29" t="n">
-        <v>802</v>
+        <v>775</v>
       </c>
       <c r="J29" t="n">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="K29" t="n">
-        <v>889</v>
+        <v>855</v>
       </c>
       <c r="L29" t="n">
-        <v>882.4</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>871</v>
+        <v>943</v>
       </c>
       <c r="C30" t="n">
-        <v>833</v>
+        <v>802</v>
       </c>
       <c r="D30" t="n">
-        <v>841</v>
+        <v>802</v>
       </c>
       <c r="E30" t="n">
-        <v>838</v>
+        <v>816</v>
       </c>
       <c r="F30" t="n">
-        <v>921</v>
+        <v>763</v>
       </c>
       <c r="G30" t="n">
-        <v>730</v>
+        <v>960</v>
       </c>
       <c r="H30" t="n">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="I30" t="n">
-        <v>847</v>
+        <v>896</v>
       </c>
       <c r="J30" t="n">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="K30" t="n">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="L30" t="n">
-        <v>845</v>
+        <v>857.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
+        <v>876</v>
+      </c>
+      <c r="C31" t="n">
+        <v>947</v>
+      </c>
+      <c r="D31" t="n">
+        <v>951</v>
+      </c>
+      <c r="E31" t="n">
         <v>950</v>
       </c>
-      <c r="C31" t="n">
-        <v>864</v>
-      </c>
-      <c r="D31" t="n">
-        <v>959</v>
-      </c>
-      <c r="E31" t="n">
-        <v>932</v>
-      </c>
       <c r="F31" t="n">
-        <v>906</v>
+        <v>835</v>
       </c>
       <c r="G31" t="n">
-        <v>907</v>
+        <v>933</v>
       </c>
       <c r="H31" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="I31" t="n">
-        <v>1019</v>
+        <v>944</v>
       </c>
       <c r="J31" t="n">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="K31" t="n">
-        <v>796</v>
+        <v>846</v>
       </c>
       <c r="L31" t="n">
-        <v>906.7</v>
+        <v>900.8</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>993</v>
+        <v>953</v>
       </c>
       <c r="C32" t="n">
-        <v>998</v>
+        <v>979</v>
       </c>
       <c r="D32" t="n">
-        <v>1037</v>
+        <v>927</v>
       </c>
       <c r="E32" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="F32" t="n">
-        <v>886</v>
+        <v>1083</v>
       </c>
       <c r="G32" t="n">
-        <v>946</v>
+        <v>1011</v>
       </c>
       <c r="H32" t="n">
-        <v>1040</v>
+        <v>1008</v>
       </c>
       <c r="I32" t="n">
-        <v>970</v>
+        <v>1091</v>
       </c>
       <c r="J32" t="n">
-        <v>1017</v>
+        <v>895</v>
       </c>
       <c r="K32" t="n">
-        <v>1018</v>
+        <v>959</v>
       </c>
       <c r="L32" t="n">
-        <v>995.5</v>
+        <v>998.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="C33" t="n">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="D33" t="n">
-        <v>889</v>
+        <v>840</v>
       </c>
       <c r="E33" t="n">
-        <v>832</v>
+        <v>810</v>
       </c>
       <c r="F33" t="n">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G33" t="n">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="H33" t="n">
-        <v>826</v>
+        <v>957</v>
       </c>
       <c r="I33" t="n">
-        <v>945</v>
+        <v>785</v>
       </c>
       <c r="J33" t="n">
-        <v>912</v>
+        <v>834</v>
       </c>
       <c r="K33" t="n">
-        <v>824</v>
+        <v>794</v>
       </c>
       <c r="L33" t="n">
-        <v>879.9</v>
+        <v>857.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>817</v>
+        <v>889</v>
       </c>
       <c r="C34" t="n">
-        <v>929</v>
+        <v>946</v>
       </c>
       <c r="D34" t="n">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="E34" t="n">
-        <v>874</v>
+        <v>957</v>
       </c>
       <c r="F34" t="n">
-        <v>788</v>
+        <v>1018</v>
       </c>
       <c r="G34" t="n">
-        <v>868</v>
+        <v>892</v>
       </c>
       <c r="H34" t="n">
-        <v>836</v>
+        <v>879</v>
       </c>
       <c r="I34" t="n">
-        <v>893</v>
+        <v>862</v>
       </c>
       <c r="J34" t="n">
-        <v>1031</v>
+        <v>915</v>
       </c>
       <c r="K34" t="n">
-        <v>886</v>
+        <v>1111</v>
       </c>
       <c r="L34" t="n">
-        <v>885</v>
+        <v>940.3</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>918</v>
+        <v>1037</v>
       </c>
       <c r="C35" t="n">
-        <v>878</v>
+        <v>966</v>
       </c>
       <c r="D35" t="n">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="E35" t="n">
-        <v>810</v>
+        <v>866</v>
       </c>
       <c r="F35" t="n">
-        <v>953</v>
+        <v>893</v>
       </c>
       <c r="G35" t="n">
-        <v>988</v>
+        <v>913</v>
       </c>
       <c r="H35" t="n">
-        <v>956</v>
+        <v>1004</v>
       </c>
       <c r="I35" t="n">
-        <v>986</v>
+        <v>865</v>
       </c>
       <c r="J35" t="n">
-        <v>954</v>
+        <v>891</v>
       </c>
       <c r="K35" t="n">
-        <v>882</v>
+        <v>959</v>
       </c>
       <c r="L35" t="n">
-        <v>923.9</v>
+        <v>929</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>896</v>
+        <v>845</v>
       </c>
       <c r="C36" t="n">
-        <v>934</v>
+        <v>1083</v>
       </c>
       <c r="D36" t="n">
-        <v>945</v>
+        <v>773</v>
       </c>
       <c r="E36" t="n">
-        <v>1030</v>
+        <v>871</v>
       </c>
       <c r="F36" t="n">
-        <v>1037</v>
+        <v>920</v>
       </c>
       <c r="G36" t="n">
-        <v>920</v>
+        <v>1035</v>
       </c>
       <c r="H36" t="n">
-        <v>862</v>
+        <v>892</v>
       </c>
       <c r="I36" t="n">
-        <v>814</v>
+        <v>1209</v>
       </c>
       <c r="J36" t="n">
-        <v>900</v>
+        <v>827</v>
       </c>
       <c r="K36" t="n">
-        <v>792</v>
+        <v>855</v>
       </c>
       <c r="L36" t="n">
-        <v>913</v>
+        <v>931</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="C37" t="n">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="D37" t="n">
-        <v>1013</v>
+        <v>833</v>
       </c>
       <c r="E37" t="n">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="F37" t="n">
-        <v>941</v>
+        <v>920</v>
       </c>
       <c r="G37" t="n">
-        <v>798</v>
+        <v>984</v>
       </c>
       <c r="H37" t="n">
-        <v>884</v>
+        <v>962</v>
       </c>
       <c r="I37" t="n">
-        <v>884</v>
+        <v>1004</v>
       </c>
       <c r="J37" t="n">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="K37" t="n">
-        <v>875</v>
+        <v>932</v>
       </c>
       <c r="L37" t="n">
-        <v>921.1</v>
+        <v>943.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>771</v>
+        <v>795</v>
       </c>
       <c r="C38" t="n">
-        <v>763</v>
+        <v>854</v>
       </c>
       <c r="D38" t="n">
+        <v>801</v>
+      </c>
+      <c r="E38" t="n">
+        <v>766</v>
+      </c>
+      <c r="F38" t="n">
+        <v>880</v>
+      </c>
+      <c r="G38" t="n">
+        <v>922</v>
+      </c>
+      <c r="H38" t="n">
         <v>870</v>
       </c>
-      <c r="E38" t="n">
-        <v>853</v>
-      </c>
-      <c r="F38" t="n">
-        <v>774</v>
-      </c>
-      <c r="G38" t="n">
-        <v>932</v>
-      </c>
-      <c r="H38" t="n">
-        <v>795</v>
-      </c>
       <c r="I38" t="n">
-        <v>856</v>
+        <v>741</v>
       </c>
       <c r="J38" t="n">
-        <v>831</v>
+        <v>859</v>
       </c>
       <c r="K38" t="n">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="L38" t="n">
-        <v>828.3</v>
+        <v>835.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>885</v>
+        <v>821</v>
       </c>
       <c r="C39" t="n">
-        <v>811</v>
+        <v>899</v>
       </c>
       <c r="D39" t="n">
-        <v>859</v>
+        <v>903</v>
       </c>
       <c r="E39" t="n">
-        <v>834</v>
+        <v>979</v>
       </c>
       <c r="F39" t="n">
-        <v>861</v>
+        <v>936</v>
       </c>
       <c r="G39" t="n">
-        <v>995</v>
+        <v>884</v>
       </c>
       <c r="H39" t="n">
-        <v>914</v>
+        <v>789</v>
       </c>
       <c r="I39" t="n">
-        <v>890</v>
+        <v>939</v>
       </c>
       <c r="J39" t="n">
-        <v>912</v>
+        <v>884</v>
       </c>
       <c r="K39" t="n">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="L39" t="n">
-        <v>881.8</v>
+        <v>888.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>874</v>
+        <v>929</v>
       </c>
       <c r="C40" t="n">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D40" t="n">
-        <v>819</v>
+        <v>784</v>
       </c>
       <c r="E40" t="n">
-        <v>851</v>
+        <v>718</v>
       </c>
       <c r="F40" t="n">
-        <v>797</v>
+        <v>890</v>
       </c>
       <c r="G40" t="n">
-        <v>769</v>
+        <v>734</v>
       </c>
       <c r="H40" t="n">
-        <v>817</v>
+        <v>861</v>
       </c>
       <c r="I40" t="n">
-        <v>774</v>
+        <v>849</v>
       </c>
       <c r="J40" t="n">
-        <v>770</v>
+        <v>872</v>
       </c>
       <c r="K40" t="n">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L40" t="n">
-        <v>801.5</v>
+        <v>817.8</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>757</v>
+        <v>842</v>
       </c>
       <c r="C41" t="n">
-        <v>808</v>
+        <v>869</v>
       </c>
       <c r="D41" t="n">
-        <v>887</v>
+        <v>722</v>
       </c>
       <c r="E41" t="n">
-        <v>869</v>
+        <v>742</v>
       </c>
       <c r="F41" t="n">
-        <v>813</v>
+        <v>727</v>
       </c>
       <c r="G41" t="n">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="H41" t="n">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="I41" t="n">
-        <v>765</v>
+        <v>827</v>
       </c>
       <c r="J41" t="n">
-        <v>846</v>
+        <v>807</v>
       </c>
       <c r="K41" t="n">
-        <v>781</v>
+        <v>817</v>
       </c>
       <c r="L41" t="n">
-        <v>809.2</v>
+        <v>793.8</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>918</v>
+        <v>826</v>
       </c>
       <c r="C42" t="n">
-        <v>1003</v>
+        <v>861</v>
       </c>
       <c r="D42" t="n">
-        <v>811</v>
+        <v>847</v>
       </c>
       <c r="E42" t="n">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="F42" t="n">
-        <v>904</v>
+        <v>848</v>
       </c>
       <c r="G42" t="n">
-        <v>861</v>
+        <v>738</v>
       </c>
       <c r="H42" t="n">
-        <v>817</v>
+        <v>757</v>
       </c>
       <c r="I42" t="n">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="J42" t="n">
-        <v>809</v>
+        <v>827</v>
       </c>
       <c r="K42" t="n">
-        <v>1012</v>
+        <v>847</v>
       </c>
       <c r="L42" t="n">
-        <v>885.6</v>
+        <v>829.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="C43" t="n">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="D43" t="n">
-        <v>932</v>
+        <v>881</v>
       </c>
       <c r="E43" t="n">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F43" t="n">
-        <v>747</v>
+        <v>830</v>
       </c>
       <c r="G43" t="n">
-        <v>1001</v>
+        <v>817</v>
       </c>
       <c r="H43" t="n">
-        <v>831</v>
+        <v>867</v>
       </c>
       <c r="I43" t="n">
-        <v>817</v>
+        <v>788</v>
       </c>
       <c r="J43" t="n">
-        <v>937</v>
+        <v>1019</v>
       </c>
       <c r="K43" t="n">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="L43" t="n">
-        <v>870.2</v>
+        <v>863.2</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>862</v>
+        <v>834</v>
       </c>
       <c r="C44" t="n">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="D44" t="n">
-        <v>856</v>
+        <v>748</v>
       </c>
       <c r="E44" t="n">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="F44" t="n">
-        <v>854</v>
+        <v>829</v>
       </c>
       <c r="G44" t="n">
-        <v>822</v>
+        <v>766</v>
       </c>
       <c r="H44" t="n">
-        <v>856</v>
+        <v>726</v>
       </c>
       <c r="I44" t="n">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="J44" t="n">
-        <v>845</v>
+        <v>736</v>
       </c>
       <c r="K44" t="n">
-        <v>870</v>
+        <v>812</v>
       </c>
       <c r="L44" t="n">
-        <v>840.5</v>
+        <v>792.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>936</v>
+        <v>1215</v>
       </c>
       <c r="C45" t="n">
-        <v>1041</v>
+        <v>926</v>
       </c>
       <c r="D45" t="n">
-        <v>948</v>
+        <v>907</v>
       </c>
       <c r="E45" t="n">
-        <v>1045</v>
+        <v>971</v>
       </c>
       <c r="F45" t="n">
-        <v>969</v>
+        <v>1073</v>
       </c>
       <c r="G45" t="n">
-        <v>1039</v>
+        <v>1064</v>
       </c>
       <c r="H45" t="n">
-        <v>1044</v>
+        <v>956</v>
       </c>
       <c r="I45" t="n">
-        <v>1036</v>
+        <v>1061</v>
       </c>
       <c r="J45" t="n">
-        <v>1054</v>
+        <v>1137</v>
       </c>
       <c r="K45" t="n">
-        <v>993</v>
+        <v>956</v>
       </c>
       <c r="L45" t="n">
-        <v>1010.5</v>
+        <v>1026.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1006</v>
+        <v>966</v>
       </c>
       <c r="C46" t="n">
-        <v>883</v>
+        <v>774</v>
       </c>
       <c r="D46" t="n">
-        <v>945</v>
+        <v>748</v>
       </c>
       <c r="E46" t="n">
-        <v>947</v>
+        <v>981</v>
       </c>
       <c r="F46" t="n">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="G46" t="n">
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="H46" t="n">
-        <v>918</v>
+        <v>844</v>
       </c>
       <c r="I46" t="n">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="J46" t="n">
-        <v>958</v>
+        <v>790</v>
       </c>
       <c r="K46" t="n">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="L46" t="n">
-        <v>937.8</v>
+        <v>891.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>972</v>
+        <v>916</v>
       </c>
       <c r="C47" t="n">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="D47" t="n">
-        <v>831</v>
+        <v>968</v>
       </c>
       <c r="E47" t="n">
-        <v>958</v>
+        <v>873</v>
       </c>
       <c r="F47" t="n">
-        <v>919</v>
+        <v>848</v>
       </c>
       <c r="G47" t="n">
-        <v>873</v>
+        <v>1086</v>
       </c>
       <c r="H47" t="n">
-        <v>818</v>
+        <v>914</v>
       </c>
       <c r="I47" t="n">
-        <v>1008</v>
+        <v>965</v>
       </c>
       <c r="J47" t="n">
-        <v>955</v>
+        <v>929</v>
       </c>
       <c r="K47" t="n">
-        <v>909</v>
+        <v>1156</v>
       </c>
       <c r="L47" t="n">
-        <v>919</v>
+        <v>961.3</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>701</v>
+        <v>779</v>
       </c>
       <c r="C48" t="n">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D48" t="n">
-        <v>812</v>
+        <v>711</v>
       </c>
       <c r="E48" t="n">
+        <v>850</v>
+      </c>
+      <c r="F48" t="n">
+        <v>763</v>
+      </c>
+      <c r="G48" t="n">
+        <v>784</v>
+      </c>
+      <c r="H48" t="n">
         <v>767</v>
       </c>
-      <c r="F48" t="n">
-        <v>860</v>
-      </c>
-      <c r="G48" t="n">
-        <v>883</v>
-      </c>
-      <c r="H48" t="n">
-        <v>835</v>
-      </c>
       <c r="I48" t="n">
-        <v>811</v>
+        <v>899</v>
       </c>
       <c r="J48" t="n">
-        <v>923</v>
+        <v>768</v>
       </c>
       <c r="K48" t="n">
-        <v>879</v>
+        <v>769</v>
       </c>
       <c r="L48" t="n">
-        <v>822.3</v>
+        <v>784.6</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C49" t="n">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="D49" t="n">
-        <v>876</v>
+        <v>974</v>
       </c>
       <c r="E49" t="n">
-        <v>966</v>
+        <v>856</v>
       </c>
       <c r="F49" t="n">
-        <v>834</v>
+        <v>942</v>
       </c>
       <c r="G49" t="n">
-        <v>878</v>
+        <v>827</v>
       </c>
       <c r="H49" t="n">
-        <v>946</v>
+        <v>919</v>
       </c>
       <c r="I49" t="n">
-        <v>909</v>
+        <v>801</v>
       </c>
       <c r="J49" t="n">
-        <v>807</v>
+        <v>977</v>
       </c>
       <c r="K49" t="n">
-        <v>879</v>
+        <v>830</v>
       </c>
       <c r="L49" t="n">
-        <v>884.4</v>
+        <v>887.2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>862</v>
+        <v>1026</v>
       </c>
       <c r="C50" t="n">
-        <v>1053</v>
+        <v>868</v>
       </c>
       <c r="D50" t="n">
-        <v>977</v>
+        <v>873</v>
       </c>
       <c r="E50" t="n">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="F50" t="n">
-        <v>854</v>
+        <v>922</v>
       </c>
       <c r="G50" t="n">
-        <v>930</v>
+        <v>906</v>
       </c>
       <c r="H50" t="n">
-        <v>840</v>
+        <v>958</v>
       </c>
       <c r="I50" t="n">
-        <v>940</v>
+        <v>909</v>
       </c>
       <c r="J50" t="n">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="K50" t="n">
-        <v>840</v>
+        <v>1048</v>
       </c>
       <c r="L50" t="n">
-        <v>908.7</v>
+        <v>930.3</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>810</v>
+        <v>838</v>
       </c>
       <c r="C51" t="n">
-        <v>859</v>
+        <v>974</v>
       </c>
       <c r="D51" t="n">
-        <v>933</v>
+        <v>884</v>
       </c>
       <c r="E51" t="n">
-        <v>890</v>
+        <v>919</v>
       </c>
       <c r="F51" t="n">
-        <v>910</v>
+        <v>867</v>
       </c>
       <c r="G51" t="n">
-        <v>896</v>
+        <v>864</v>
       </c>
       <c r="H51" t="n">
-        <v>808</v>
+        <v>781</v>
       </c>
       <c r="I51" t="n">
-        <v>785</v>
+        <v>886</v>
       </c>
       <c r="J51" t="n">
-        <v>1021</v>
+        <v>894</v>
       </c>
       <c r="K51" t="n">
-        <v>801</v>
+        <v>883</v>
       </c>
       <c r="L51" t="n">
-        <v>871.3</v>
+        <v>879</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>892.78</v>
+        <v>899.24</v>
       </c>
       <c r="C52" t="n">
-        <v>884.2</v>
+        <v>876.96</v>
       </c>
       <c r="D52" t="n">
-        <v>899.86</v>
+        <v>858.08</v>
       </c>
       <c r="E52" t="n">
-        <v>898.64</v>
+        <v>877.9400000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>881.52</v>
+        <v>887.3200000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>893.98</v>
+        <v>888.92</v>
       </c>
       <c r="H52" t="n">
-        <v>875.5599999999999</v>
+        <v>877.9</v>
       </c>
       <c r="I52" t="n">
-        <v>886.66</v>
+        <v>913.86</v>
       </c>
       <c r="J52" t="n">
-        <v>903.04</v>
+        <v>894.2</v>
       </c>
       <c r="K52" t="n">
-        <v>874.58</v>
+        <v>897.74</v>
       </c>
       <c r="L52" t="n">
-        <v>889.082</v>
+        <v>887.216</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.449954271316528</v>
+        <v>7.943889379501343</v>
       </c>
       <c r="C2" t="n">
-        <v>8.406483888626099</v>
+        <v>7.903357267379761</v>
       </c>
       <c r="D2" t="n">
-        <v>7.847687959671021</v>
+        <v>8.753686189651489</v>
       </c>
       <c r="E2" t="n">
-        <v>8.840348720550537</v>
+        <v>7.9731764793396</v>
       </c>
       <c r="F2" t="n">
-        <v>7.440091133117676</v>
+        <v>8.411557197570801</v>
       </c>
       <c r="G2" t="n">
-        <v>7.273414611816406</v>
+        <v>7.97669506072998</v>
       </c>
       <c r="H2" t="n">
-        <v>7.012013912200928</v>
+        <v>7.835013866424561</v>
       </c>
       <c r="I2" t="n">
-        <v>7.151126861572266</v>
+        <v>7.854943513870239</v>
       </c>
       <c r="J2" t="n">
-        <v>7.775897979736328</v>
+        <v>7.658987522125244</v>
       </c>
       <c r="K2" t="n">
-        <v>7.467466115951538</v>
+        <v>8.150705814361572</v>
       </c>
       <c r="L2" t="n">
-        <v>7.666448545455933</v>
+        <v>8.046201229095459</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>7.482392311096191</v>
+        <v>8.538289070129395</v>
       </c>
       <c r="C3" t="n">
-        <v>7.560389041900635</v>
+        <v>7.968254804611206</v>
       </c>
       <c r="D3" t="n">
-        <v>7.51704478263855</v>
+        <v>7.792226076126099</v>
       </c>
       <c r="E3" t="n">
-        <v>7.625705480575562</v>
+        <v>8.882373094558716</v>
       </c>
       <c r="F3" t="n">
-        <v>7.610594749450684</v>
+        <v>8.094449758529663</v>
       </c>
       <c r="G3" t="n">
-        <v>7.57670783996582</v>
+        <v>7.637115955352783</v>
       </c>
       <c r="H3" t="n">
-        <v>7.521645069122314</v>
+        <v>8.109382152557373</v>
       </c>
       <c r="I3" t="n">
-        <v>7.509964942932129</v>
+        <v>8.184673070907593</v>
       </c>
       <c r="J3" t="n">
-        <v>8.293058395385742</v>
+        <v>7.79222846031189</v>
       </c>
       <c r="K3" t="n">
-        <v>7.811501264572144</v>
+        <v>7.851064443588257</v>
       </c>
       <c r="L3" t="n">
-        <v>7.650900387763977</v>
+        <v>8.085005688667298</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.530935287475586</v>
+        <v>8.618002414703369</v>
       </c>
       <c r="C4" t="n">
-        <v>9.109927177429199</v>
+        <v>8.238970994949341</v>
       </c>
       <c r="D4" t="n">
-        <v>8.319179058074951</v>
+        <v>10.0427827835083</v>
       </c>
       <c r="E4" t="n">
-        <v>8.602711915969849</v>
+        <v>8.02910590171814</v>
       </c>
       <c r="F4" t="n">
-        <v>7.534770488739014</v>
+        <v>8.087458848953247</v>
       </c>
       <c r="G4" t="n">
-        <v>7.490648984909058</v>
+        <v>8.508364915847778</v>
       </c>
       <c r="H4" t="n">
-        <v>7.848868370056152</v>
+        <v>7.586749792098999</v>
       </c>
       <c r="I4" t="n">
-        <v>7.608035087585449</v>
+        <v>9.034955501556396</v>
       </c>
       <c r="J4" t="n">
-        <v>7.883843660354614</v>
+        <v>8.192187309265137</v>
       </c>
       <c r="K4" t="n">
-        <v>7.821999073028564</v>
+        <v>7.947355985641479</v>
       </c>
       <c r="L4" t="n">
-        <v>7.975091910362243</v>
+        <v>8.428593444824219</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>6.83980393409729</v>
+        <v>9.165648221969604</v>
       </c>
       <c r="C5" t="n">
-        <v>6.954340219497681</v>
+        <v>8.011128902435303</v>
       </c>
       <c r="D5" t="n">
-        <v>7.26014232635498</v>
+        <v>9.97803521156311</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7554931640625</v>
+        <v>7.032358884811401</v>
       </c>
       <c r="F5" t="n">
-        <v>6.96987509727478</v>
+        <v>7.3927903175354</v>
       </c>
       <c r="G5" t="n">
-        <v>7.353340148925781</v>
+        <v>7.708344221115112</v>
       </c>
       <c r="H5" t="n">
-        <v>7.597829580307007</v>
+        <v>7.772163152694702</v>
       </c>
       <c r="I5" t="n">
-        <v>8.157605171203613</v>
+        <v>8.44050407409668</v>
       </c>
       <c r="J5" t="n">
-        <v>8.219727993011475</v>
+        <v>8.031504154205322</v>
       </c>
       <c r="K5" t="n">
-        <v>6.889817237854004</v>
+        <v>7.259000539779663</v>
       </c>
       <c r="L5" t="n">
-        <v>7.299797487258911</v>
+        <v>8.079147768020629</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>8.669486284255981</v>
+        <v>7.63758397102356</v>
       </c>
       <c r="C6" t="n">
-        <v>7.381491422653198</v>
+        <v>8.325260162353516</v>
       </c>
       <c r="D6" t="n">
-        <v>8.665900707244873</v>
+        <v>7.81707501411438</v>
       </c>
       <c r="E6" t="n">
-        <v>7.513988256454468</v>
+        <v>8.458944797515869</v>
       </c>
       <c r="F6" t="n">
-        <v>7.135266780853271</v>
+        <v>7.874912977218628</v>
       </c>
       <c r="G6" t="n">
-        <v>8.313198804855347</v>
+        <v>8.43248724937439</v>
       </c>
       <c r="H6" t="n">
-        <v>7.33756947517395</v>
+        <v>7.86544394493103</v>
       </c>
       <c r="I6" t="n">
-        <v>7.985459804534912</v>
+        <v>8.277899742126465</v>
       </c>
       <c r="J6" t="n">
-        <v>8.555022954940796</v>
+        <v>8.635002613067627</v>
       </c>
       <c r="K6" t="n">
-        <v>7.283314943313599</v>
+        <v>8.018068075180054</v>
       </c>
       <c r="L6" t="n">
-        <v>7.88406994342804</v>
+        <v>8.134267854690552</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.481285810470581</v>
+        <v>7.746721744537354</v>
       </c>
       <c r="C7" t="n">
-        <v>7.464382410049438</v>
+        <v>8.130793571472168</v>
       </c>
       <c r="D7" t="n">
-        <v>7.681021451950073</v>
+        <v>8.408564567565918</v>
       </c>
       <c r="E7" t="n">
-        <v>9.448801517486572</v>
+        <v>8.321941614151001</v>
       </c>
       <c r="F7" t="n">
-        <v>7.995899438858032</v>
+        <v>8.500014305114746</v>
       </c>
       <c r="G7" t="n">
-        <v>8.94063138961792</v>
+        <v>8.171700716018677</v>
       </c>
       <c r="H7" t="n">
-        <v>8.127932548522949</v>
+        <v>8.271413564682007</v>
       </c>
       <c r="I7" t="n">
-        <v>9.117513179779053</v>
+        <v>8.023542881011963</v>
       </c>
       <c r="J7" t="n">
-        <v>7.462120771408081</v>
+        <v>8.447463512420654</v>
       </c>
       <c r="K7" t="n">
-        <v>8.091592311859131</v>
+        <v>9.432975769042969</v>
       </c>
       <c r="L7" t="n">
-        <v>8.281118083000184</v>
+        <v>8.345513224601746</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.515047311782837</v>
+        <v>7.88482403755188</v>
       </c>
       <c r="C8" t="n">
-        <v>7.353646278381348</v>
+        <v>8.799087047576904</v>
       </c>
       <c r="D8" t="n">
-        <v>7.643689632415771</v>
+        <v>7.641189336776733</v>
       </c>
       <c r="E8" t="n">
-        <v>7.475969314575195</v>
+        <v>7.620157957077026</v>
       </c>
       <c r="F8" t="n">
-        <v>7.244632482528687</v>
+        <v>8.039044618606567</v>
       </c>
       <c r="G8" t="n">
-        <v>7.165451765060425</v>
+        <v>7.772278785705566</v>
       </c>
       <c r="H8" t="n">
-        <v>8.180095434188843</v>
+        <v>7.942805767059326</v>
       </c>
       <c r="I8" t="n">
-        <v>7.573111057281494</v>
+        <v>7.857063770294189</v>
       </c>
       <c r="J8" t="n">
-        <v>6.953818798065186</v>
+        <v>8.425059080123901</v>
       </c>
       <c r="K8" t="n">
-        <v>7.441725254058838</v>
+        <v>7.569774627685547</v>
       </c>
       <c r="L8" t="n">
-        <v>7.454718732833863</v>
+        <v>7.955128502845764</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.251243114471436</v>
+        <v>9.648923635482788</v>
       </c>
       <c r="C9" t="n">
-        <v>8.200589179992676</v>
+        <v>8.636034250259399</v>
       </c>
       <c r="D9" t="n">
-        <v>7.827989339828491</v>
+        <v>8.174224615097046</v>
       </c>
       <c r="E9" t="n">
-        <v>7.968255281448364</v>
+        <v>8.215341329574585</v>
       </c>
       <c r="F9" t="n">
-        <v>8.21033501625061</v>
+        <v>9.611279249191284</v>
       </c>
       <c r="G9" t="n">
-        <v>8.729543209075928</v>
+        <v>8.160701751708984</v>
       </c>
       <c r="H9" t="n">
-        <v>7.721045970916748</v>
+        <v>8.025528192520142</v>
       </c>
       <c r="I9" t="n">
-        <v>8.14582633972168</v>
+        <v>9.363160371780396</v>
       </c>
       <c r="J9" t="n">
-        <v>7.839821815490723</v>
+        <v>8.296347618103027</v>
       </c>
       <c r="K9" t="n">
-        <v>7.877535820007324</v>
+        <v>8.309307813644409</v>
       </c>
       <c r="L9" t="n">
-        <v>8.077218508720398</v>
+        <v>8.644084882736205</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.486910581588745</v>
+        <v>6.956504583358765</v>
       </c>
       <c r="C10" t="n">
-        <v>6.458328723907471</v>
+        <v>7.255616664886475</v>
       </c>
       <c r="D10" t="n">
-        <v>6.657334566116333</v>
+        <v>7.000290870666504</v>
       </c>
       <c r="E10" t="n">
-        <v>7.179684638977051</v>
+        <v>9.498728275299072</v>
       </c>
       <c r="F10" t="n">
-        <v>7.69446063041687</v>
+        <v>6.975231409072876</v>
       </c>
       <c r="G10" t="n">
-        <v>6.735801458358765</v>
+        <v>7.169207811355591</v>
       </c>
       <c r="H10" t="n">
-        <v>6.667003393173218</v>
+        <v>7.104409694671631</v>
       </c>
       <c r="I10" t="n">
-        <v>6.63400936126709</v>
+        <v>6.814629316329956</v>
       </c>
       <c r="J10" t="n">
-        <v>7.470872402191162</v>
+        <v>7.097408771514893</v>
       </c>
       <c r="K10" t="n">
-        <v>6.522527933120728</v>
+        <v>7.164808988571167</v>
       </c>
       <c r="L10" t="n">
-        <v>6.850693368911744</v>
+        <v>7.303683638572693</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.470018148422241</v>
+        <v>8.762134075164795</v>
       </c>
       <c r="C11" t="n">
-        <v>6.492133855819702</v>
+        <v>6.953295230865479</v>
       </c>
       <c r="D11" t="n">
-        <v>7.259336948394775</v>
+        <v>6.802155494689941</v>
       </c>
       <c r="E11" t="n">
-        <v>6.766153335571289</v>
+        <v>7.259995460510254</v>
       </c>
       <c r="F11" t="n">
-        <v>6.549200773239136</v>
+        <v>6.942798614501953</v>
       </c>
       <c r="G11" t="n">
-        <v>6.968960285186768</v>
+        <v>7.029070615768433</v>
       </c>
       <c r="H11" t="n">
-        <v>7.08291220664978</v>
+        <v>8.146716833114624</v>
       </c>
       <c r="I11" t="n">
-        <v>8.400481939315796</v>
+        <v>6.582256555557251</v>
       </c>
       <c r="J11" t="n">
-        <v>6.426172494888306</v>
+        <v>7.683896780014038</v>
       </c>
       <c r="K11" t="n">
-        <v>6.293295621871948</v>
+        <v>7.311972856521606</v>
       </c>
       <c r="L11" t="n">
-        <v>6.970866560935974</v>
+        <v>7.347429251670837</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.10016942024231</v>
+        <v>7.579292058944702</v>
       </c>
       <c r="C12" t="n">
-        <v>7.267009258270264</v>
+        <v>7.253138065338135</v>
       </c>
       <c r="D12" t="n">
-        <v>6.807800054550171</v>
+        <v>7.540898561477661</v>
       </c>
       <c r="E12" t="n">
-        <v>8.096625328063965</v>
+        <v>7.088034152984619</v>
       </c>
       <c r="F12" t="n">
-        <v>7.22757363319397</v>
+        <v>7.471539497375488</v>
       </c>
       <c r="G12" t="n">
-        <v>6.870638132095337</v>
+        <v>7.666525840759277</v>
       </c>
       <c r="H12" t="n">
-        <v>7.113576650619507</v>
+        <v>7.242131233215332</v>
       </c>
       <c r="I12" t="n">
-        <v>6.618126392364502</v>
+        <v>7.959276437759399</v>
       </c>
       <c r="J12" t="n">
-        <v>6.591415405273438</v>
+        <v>7.740348815917969</v>
       </c>
       <c r="K12" t="n">
-        <v>6.634729385375977</v>
+        <v>7.946141004562378</v>
       </c>
       <c r="L12" t="n">
-        <v>7.032766366004944</v>
+        <v>7.548732566833496</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.052008152008057</v>
+        <v>8.714837074279785</v>
       </c>
       <c r="C13" t="n">
-        <v>7.097478151321411</v>
+        <v>7.950313568115234</v>
       </c>
       <c r="D13" t="n">
-        <v>8.687747955322266</v>
+        <v>8.919256687164307</v>
       </c>
       <c r="E13" t="n">
-        <v>7.104951143264771</v>
+        <v>7.269076347351074</v>
       </c>
       <c r="F13" t="n">
-        <v>9.212117195129395</v>
+        <v>7.676503896713257</v>
       </c>
       <c r="G13" t="n">
-        <v>6.84576416015625</v>
+        <v>7.67154598236084</v>
       </c>
       <c r="H13" t="n">
-        <v>6.850308656692505</v>
+        <v>8.18517541885376</v>
       </c>
       <c r="I13" t="n">
-        <v>7.045759439468384</v>
+        <v>7.61557674407959</v>
       </c>
       <c r="J13" t="n">
-        <v>8.511275053024292</v>
+        <v>8.861407041549683</v>
       </c>
       <c r="K13" t="n">
-        <v>8.853062391281128</v>
+        <v>7.380167961120605</v>
       </c>
       <c r="L13" t="n">
-        <v>7.726047229766846</v>
+        <v>8.024386072158814</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.940611124038696</v>
+        <v>8.378652095794678</v>
       </c>
       <c r="C14" t="n">
-        <v>7.605216979980469</v>
+        <v>8.303318023681641</v>
       </c>
       <c r="D14" t="n">
-        <v>7.230865240097046</v>
+        <v>7.966164112091064</v>
       </c>
       <c r="E14" t="n">
-        <v>7.685466289520264</v>
+        <v>8.273443222045898</v>
       </c>
       <c r="F14" t="n">
-        <v>7.709649801254272</v>
+        <v>8.625000476837158</v>
       </c>
       <c r="G14" t="n">
-        <v>7.628417015075684</v>
+        <v>8.131828308105469</v>
       </c>
       <c r="H14" t="n">
-        <v>7.932009220123291</v>
+        <v>8.799634456634521</v>
       </c>
       <c r="I14" t="n">
-        <v>8.500824689865112</v>
+        <v>7.948323965072632</v>
       </c>
       <c r="J14" t="n">
-        <v>7.398961067199707</v>
+        <v>8.520787715911865</v>
       </c>
       <c r="K14" t="n">
-        <v>8.004155158996582</v>
+        <v>8.492825746536255</v>
       </c>
       <c r="L14" t="n">
-        <v>7.763617658615113</v>
+        <v>8.343997812271118</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>9.521979093551636</v>
+        <v>7.985148668289185</v>
       </c>
       <c r="C15" t="n">
-        <v>8.676131248474121</v>
+        <v>7.97669529914856</v>
       </c>
       <c r="D15" t="n">
-        <v>7.991534948348999</v>
+        <v>7.962203741073608</v>
       </c>
       <c r="E15" t="n">
-        <v>8.641862869262695</v>
+        <v>9.041454315185547</v>
       </c>
       <c r="F15" t="n">
-        <v>8.195769309997559</v>
+        <v>8.532755613327026</v>
       </c>
       <c r="G15" t="n">
-        <v>7.642601013183594</v>
+        <v>8.461419105529785</v>
       </c>
       <c r="H15" t="n">
-        <v>9.159647941589355</v>
+        <v>8.157220363616943</v>
       </c>
       <c r="I15" t="n">
-        <v>8.462327480316162</v>
+        <v>9.877816438674927</v>
       </c>
       <c r="J15" t="n">
-        <v>8.176249265670776</v>
+        <v>9.193572998046875</v>
       </c>
       <c r="K15" t="n">
-        <v>7.659470796585083</v>
+        <v>8.113536357879639</v>
       </c>
       <c r="L15" t="n">
-        <v>8.412757396697998</v>
+        <v>8.53018229007721</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>6.977630138397217</v>
+        <v>7.255520343780518</v>
       </c>
       <c r="C16" t="n">
-        <v>7.206443071365356</v>
+        <v>7.328821897506714</v>
       </c>
       <c r="D16" t="n">
-        <v>7.55611777305603</v>
+        <v>7.347266912460327</v>
       </c>
       <c r="E16" t="n">
-        <v>7.733413219451904</v>
+        <v>7.347760915756226</v>
       </c>
       <c r="F16" t="n">
-        <v>6.718455791473389</v>
+        <v>8.215101957321167</v>
       </c>
       <c r="G16" t="n">
-        <v>6.788644075393677</v>
+        <v>8.338264465332031</v>
       </c>
       <c r="H16" t="n">
-        <v>7.053851127624512</v>
+        <v>7.222586393356323</v>
       </c>
       <c r="I16" t="n">
-        <v>6.966139554977417</v>
+        <v>7.704888105392456</v>
       </c>
       <c r="J16" t="n">
-        <v>6.847138643264771</v>
+        <v>8.035499095916748</v>
       </c>
       <c r="K16" t="n">
-        <v>8.018007516860962</v>
+        <v>7.425070285797119</v>
       </c>
       <c r="L16" t="n">
-        <v>7.186584091186523</v>
+        <v>7.622078037261963</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.43070912361145</v>
+        <v>7.799613237380981</v>
       </c>
       <c r="C17" t="n">
-        <v>9.63623046875</v>
+        <v>8.24547290802002</v>
       </c>
       <c r="D17" t="n">
-        <v>8.9228515625</v>
+        <v>9.269359588623047</v>
       </c>
       <c r="E17" t="n">
-        <v>7.408184766769409</v>
+        <v>8.42553448677063</v>
       </c>
       <c r="F17" t="n">
-        <v>8.103437423706055</v>
+        <v>7.872457027435303</v>
       </c>
       <c r="G17" t="n">
-        <v>7.538518667221069</v>
+        <v>7.772712707519531</v>
       </c>
       <c r="H17" t="n">
-        <v>7.458608388900757</v>
+        <v>8.770647048950195</v>
       </c>
       <c r="I17" t="n">
-        <v>8.305236339569092</v>
+        <v>7.841025829315186</v>
       </c>
       <c r="J17" t="n">
-        <v>7.597582817077637</v>
+        <v>8.357187271118164</v>
       </c>
       <c r="K17" t="n">
-        <v>7.555635929107666</v>
+        <v>8.046047449111938</v>
       </c>
       <c r="L17" t="n">
-        <v>7.995699548721314</v>
+        <v>8.2400057554245</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.563196897506714</v>
+        <v>9.822977781295776</v>
       </c>
       <c r="C18" t="n">
-        <v>8.327765703201294</v>
+        <v>9.174139261245728</v>
       </c>
       <c r="D18" t="n">
-        <v>9.311544895172119</v>
+        <v>9.112256526947021</v>
       </c>
       <c r="E18" t="n">
-        <v>8.715451717376709</v>
+        <v>9.586554765701294</v>
       </c>
       <c r="F18" t="n">
-        <v>8.598768472671509</v>
+        <v>9.430975675582886</v>
       </c>
       <c r="G18" t="n">
-        <v>9.293759346008301</v>
+        <v>8.54572582244873</v>
       </c>
       <c r="H18" t="n">
-        <v>9.615302801132202</v>
+        <v>8.89385461807251</v>
       </c>
       <c r="I18" t="n">
-        <v>9.001588344573975</v>
+        <v>9.983544588088989</v>
       </c>
       <c r="J18" t="n">
-        <v>8.503592014312744</v>
+        <v>9.336755514144897</v>
       </c>
       <c r="K18" t="n">
-        <v>8.808514595031738</v>
+        <v>8.578631401062012</v>
       </c>
       <c r="L18" t="n">
-        <v>8.97394847869873</v>
+        <v>9.246541595458984</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.442336559295654</v>
+        <v>6.622148036956787</v>
       </c>
       <c r="C19" t="n">
-        <v>6.109987258911133</v>
+        <v>7.268646717071533</v>
       </c>
       <c r="D19" t="n">
-        <v>7.354347944259644</v>
+        <v>7.295566082000732</v>
       </c>
       <c r="E19" t="n">
-        <v>6.317161321640015</v>
+        <v>6.729328632354736</v>
       </c>
       <c r="F19" t="n">
-        <v>6.659076690673828</v>
+        <v>7.224105596542358</v>
       </c>
       <c r="G19" t="n">
-        <v>6.372441530227661</v>
+        <v>6.373286724090576</v>
       </c>
       <c r="H19" t="n">
-        <v>6.053542375564575</v>
+        <v>6.633077383041382</v>
       </c>
       <c r="I19" t="n">
-        <v>6.831106662750244</v>
+        <v>7.32282829284668</v>
       </c>
       <c r="J19" t="n">
-        <v>6.06220531463623</v>
+        <v>7.20962119102478</v>
       </c>
       <c r="K19" t="n">
-        <v>6.735992908477783</v>
+        <v>7.679957389831543</v>
       </c>
       <c r="L19" t="n">
-        <v>6.593819856643677</v>
+        <v>7.035856604576111</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>6.753201484680176</v>
+        <v>7.93427300453186</v>
       </c>
       <c r="C20" t="n">
-        <v>7.13859748840332</v>
+        <v>7.945726156234741</v>
       </c>
       <c r="D20" t="n">
-        <v>6.740210056304932</v>
+        <v>7.972187042236328</v>
       </c>
       <c r="E20" t="n">
-        <v>7.053725481033325</v>
+        <v>8.114498615264893</v>
       </c>
       <c r="F20" t="n">
-        <v>8.09794020652771</v>
+        <v>7.454999923706055</v>
       </c>
       <c r="G20" t="n">
-        <v>7.586077451705933</v>
+        <v>7.994627475738525</v>
       </c>
       <c r="H20" t="n">
-        <v>7.721086502075195</v>
+        <v>8.129866123199463</v>
       </c>
       <c r="I20" t="n">
-        <v>7.160850524902344</v>
+        <v>8.771974563598633</v>
       </c>
       <c r="J20" t="n">
-        <v>7.086577653884888</v>
+        <v>7.492408275604248</v>
       </c>
       <c r="K20" t="n">
-        <v>7.760070085525513</v>
+        <v>8.617048501968384</v>
       </c>
       <c r="L20" t="n">
-        <v>7.309833693504333</v>
+        <v>8.042760968208313</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.157151937484741</v>
+        <v>8.164682149887085</v>
       </c>
       <c r="C21" t="n">
-        <v>7.190123796463013</v>
+        <v>8.040012359619141</v>
       </c>
       <c r="D21" t="n">
-        <v>8.666544914245605</v>
+        <v>8.757148265838623</v>
       </c>
       <c r="E21" t="n">
-        <v>7.359981298446655</v>
+        <v>8.283365249633789</v>
       </c>
       <c r="F21" t="n">
-        <v>8.005539655685425</v>
+        <v>7.190180063247681</v>
       </c>
       <c r="G21" t="n">
-        <v>6.831281423568726</v>
+        <v>7.702849864959717</v>
       </c>
       <c r="H21" t="n">
-        <v>8.216132164001465</v>
+        <v>7.524343967437744</v>
       </c>
       <c r="I21" t="n">
-        <v>8.229484558105469</v>
+        <v>10.10577583312988</v>
       </c>
       <c r="J21" t="n">
-        <v>6.671571731567383</v>
+        <v>8.50394606590271</v>
       </c>
       <c r="K21" t="n">
-        <v>8.53286337852478</v>
+        <v>7.528137683868408</v>
       </c>
       <c r="L21" t="n">
-        <v>7.686067485809327</v>
+        <v>8.180044150352478</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.707578182220459</v>
+        <v>7.558745145797729</v>
       </c>
       <c r="C22" t="n">
-        <v>6.665034532546997</v>
+        <v>7.770660638809204</v>
       </c>
       <c r="D22" t="n">
-        <v>7.570450305938721</v>
+        <v>8.073924779891968</v>
       </c>
       <c r="E22" t="n">
-        <v>7.674260377883911</v>
+        <v>7.648488998413086</v>
       </c>
       <c r="F22" t="n">
-        <v>7.006815910339355</v>
+        <v>8.287367343902588</v>
       </c>
       <c r="G22" t="n">
-        <v>7.976279020309448</v>
+        <v>8.111794233322144</v>
       </c>
       <c r="H22" t="n">
-        <v>6.749425649642944</v>
+        <v>7.220561027526855</v>
       </c>
       <c r="I22" t="n">
-        <v>7.079596519470215</v>
+        <v>9.658473491668701</v>
       </c>
       <c r="J22" t="n">
-        <v>8.754912376403809</v>
+        <v>8.191130638122559</v>
       </c>
       <c r="K22" t="n">
-        <v>7.215005397796631</v>
+        <v>8.601094961166382</v>
       </c>
       <c r="L22" t="n">
-        <v>7.439935827255249</v>
+        <v>8.112224125862122</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.993673086166382</v>
+        <v>9.940148830413818</v>
       </c>
       <c r="C23" t="n">
-        <v>9.971637964248657</v>
+        <v>9.700797557830811</v>
       </c>
       <c r="D23" t="n">
-        <v>8.778191328048706</v>
+        <v>10.43240213394165</v>
       </c>
       <c r="E23" t="n">
-        <v>9.803709745407104</v>
+        <v>9.295792579650879</v>
       </c>
       <c r="F23" t="n">
-        <v>8.506190538406372</v>
+        <v>10.47677826881409</v>
       </c>
       <c r="G23" t="n">
-        <v>8.95390772819519</v>
+        <v>10.54561543464661</v>
       </c>
       <c r="H23" t="n">
-        <v>8.941587209701538</v>
+        <v>8.81352972984314</v>
       </c>
       <c r="I23" t="n">
-        <v>9.848512411117554</v>
+        <v>11.7809956073761</v>
       </c>
       <c r="J23" t="n">
-        <v>9.107918977737427</v>
+        <v>8.923763275146484</v>
       </c>
       <c r="K23" t="n">
-        <v>8.094107627868652</v>
+        <v>10.11568737030029</v>
       </c>
       <c r="L23" t="n">
-        <v>9.099943661689759</v>
+        <v>10.00255107879639</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.931514024734497</v>
+        <v>7.321858406066895</v>
       </c>
       <c r="C24" t="n">
-        <v>6.767382860183716</v>
+        <v>7.208613395690918</v>
       </c>
       <c r="D24" t="n">
-        <v>7.468243837356567</v>
+        <v>7.963200807571411</v>
       </c>
       <c r="E24" t="n">
-        <v>7.379760503768921</v>
+        <v>7.219679832458496</v>
       </c>
       <c r="F24" t="n">
-        <v>6.888944864273071</v>
+        <v>7.637144804000854</v>
       </c>
       <c r="G24" t="n">
-        <v>7.337602853775024</v>
+        <v>9.858830451965332</v>
       </c>
       <c r="H24" t="n">
-        <v>6.925010919570923</v>
+        <v>8.0251145362854</v>
       </c>
       <c r="I24" t="n">
-        <v>8.258356094360352</v>
+        <v>8.154271841049194</v>
       </c>
       <c r="J24" t="n">
-        <v>7.338797330856323</v>
+        <v>7.313446760177612</v>
       </c>
       <c r="K24" t="n">
-        <v>8.295902490615845</v>
+        <v>7.551324844360352</v>
       </c>
       <c r="L24" t="n">
-        <v>7.459151577949524</v>
+        <v>7.825348567962647</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>8.568375110626221</v>
+        <v>9.284801006317139</v>
       </c>
       <c r="C25" t="n">
-        <v>8.405012130737305</v>
+        <v>9.080856800079346</v>
       </c>
       <c r="D25" t="n">
-        <v>8.339867115020752</v>
+        <v>9.264882326126099</v>
       </c>
       <c r="E25" t="n">
-        <v>8.751972436904907</v>
+        <v>9.415521144866943</v>
       </c>
       <c r="F25" t="n">
-        <v>10.76913166046143</v>
+        <v>10.60140895843506</v>
       </c>
       <c r="G25" t="n">
-        <v>8.694483518600464</v>
+        <v>9.191577911376953</v>
       </c>
       <c r="H25" t="n">
-        <v>10.37354421615601</v>
+        <v>9.582064628601074</v>
       </c>
       <c r="I25" t="n">
-        <v>9.008527278900146</v>
+        <v>9.32375693321228</v>
       </c>
       <c r="J25" t="n">
-        <v>9.302315950393677</v>
+        <v>11.29980611801147</v>
       </c>
       <c r="K25" t="n">
-        <v>8.584902763366699</v>
+        <v>9.389072418212891</v>
       </c>
       <c r="L25" t="n">
-        <v>9.07981321811676</v>
+        <v>9.643374824523926</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.963987112045288</v>
+        <v>8.310330867767334</v>
       </c>
       <c r="C26" t="n">
-        <v>7.494630336761475</v>
+        <v>8.729255199432373</v>
       </c>
       <c r="D26" t="n">
-        <v>8.232039928436279</v>
+        <v>10.33104872703552</v>
       </c>
       <c r="E26" t="n">
-        <v>7.593441009521484</v>
+        <v>8.259932518005371</v>
       </c>
       <c r="F26" t="n">
-        <v>7.925841808319092</v>
+        <v>7.960739612579346</v>
       </c>
       <c r="G26" t="n">
-        <v>8.144483089447021</v>
+        <v>9.362618207931519</v>
       </c>
       <c r="H26" t="n">
-        <v>8.269493818283081</v>
+        <v>8.043493509292603</v>
       </c>
       <c r="I26" t="n">
-        <v>8.8542320728302</v>
+        <v>8.152203321456909</v>
       </c>
       <c r="J26" t="n">
-        <v>8.307446956634521</v>
+        <v>8.696859359741211</v>
       </c>
       <c r="K26" t="n">
-        <v>7.585355281829834</v>
+        <v>8.879851102828979</v>
       </c>
       <c r="L26" t="n">
-        <v>8.237095141410828</v>
+        <v>8.672633242607116</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.7802574634552</v>
+        <v>8.848978757858276</v>
       </c>
       <c r="C27" t="n">
-        <v>8.232913970947266</v>
+        <v>9.276358366012573</v>
       </c>
       <c r="D27" t="n">
-        <v>8.787915229797363</v>
+        <v>9.156169414520264</v>
       </c>
       <c r="E27" t="n">
-        <v>9.827763080596924</v>
+        <v>10.54356718063354</v>
       </c>
       <c r="F27" t="n">
-        <v>8.771344184875488</v>
+        <v>9.114269256591797</v>
       </c>
       <c r="G27" t="n">
-        <v>8.534359931945801</v>
+        <v>9.82095193862915</v>
       </c>
       <c r="H27" t="n">
-        <v>9.813862800598145</v>
+        <v>9.188050508499146</v>
       </c>
       <c r="I27" t="n">
-        <v>9.684460878372192</v>
+        <v>10.98601675033569</v>
       </c>
       <c r="J27" t="n">
-        <v>8.431195735931396</v>
+        <v>9.799008846282959</v>
       </c>
       <c r="K27" t="n">
-        <v>8.412275791168213</v>
+        <v>9.981080055236816</v>
       </c>
       <c r="L27" t="n">
-        <v>8.927634906768798</v>
+        <v>9.671445107460022</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.623454332351685</v>
+        <v>7.612601041793823</v>
       </c>
       <c r="C28" t="n">
-        <v>6.998110055923462</v>
+        <v>7.495399713516235</v>
       </c>
       <c r="D28" t="n">
-        <v>7.295794010162354</v>
+        <v>7.215630292892456</v>
       </c>
       <c r="E28" t="n">
-        <v>7.148276329040527</v>
+        <v>7.215595006942749</v>
       </c>
       <c r="F28" t="n">
-        <v>7.277259588241577</v>
+        <v>7.268465280532837</v>
       </c>
       <c r="G28" t="n">
-        <v>7.174679279327393</v>
+        <v>7.516869068145752</v>
       </c>
       <c r="H28" t="n">
-        <v>6.941463947296143</v>
+        <v>7.985172986984253</v>
       </c>
       <c r="I28" t="n">
-        <v>7.081192493438721</v>
+        <v>7.830053806304932</v>
       </c>
       <c r="J28" t="n">
-        <v>7.216524600982666</v>
+        <v>7.631572961807251</v>
       </c>
       <c r="K28" t="n">
-        <v>7.083704471588135</v>
+        <v>7.827571868896484</v>
       </c>
       <c r="L28" t="n">
-        <v>7.184045910835266</v>
+        <v>7.559893202781677</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.867478609085083</v>
+        <v>8.00060772895813</v>
       </c>
       <c r="C29" t="n">
-        <v>7.282456636428833</v>
+        <v>7.428074359893799</v>
       </c>
       <c r="D29" t="n">
-        <v>7.262482404708862</v>
+        <v>7.920339345932007</v>
       </c>
       <c r="E29" t="n">
-        <v>7.597578525543213</v>
+        <v>8.628020048141479</v>
       </c>
       <c r="F29" t="n">
-        <v>7.525330543518066</v>
+        <v>7.92826247215271</v>
       </c>
       <c r="G29" t="n">
-        <v>7.834494829177856</v>
+        <v>8.711755990982056</v>
       </c>
       <c r="H29" t="n">
-        <v>7.048783302307129</v>
+        <v>8.29831862449646</v>
       </c>
       <c r="I29" t="n">
-        <v>7.063722133636475</v>
+        <v>8.33191442489624</v>
       </c>
       <c r="J29" t="n">
-        <v>7.789984703063965</v>
+        <v>8.009600877761841</v>
       </c>
       <c r="K29" t="n">
-        <v>7.680155277252197</v>
+        <v>7.804589033126831</v>
       </c>
       <c r="L29" t="n">
-        <v>7.495246696472168</v>
+        <v>8.106148290634156</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.331145286560059</v>
+        <v>7.972193241119385</v>
       </c>
       <c r="C30" t="n">
-        <v>6.981203556060791</v>
+        <v>7.434064388275146</v>
       </c>
       <c r="D30" t="n">
-        <v>7.120447158813477</v>
+        <v>7.960709571838379</v>
       </c>
       <c r="E30" t="n">
-        <v>7.636993885040283</v>
+        <v>8.066424369812012</v>
       </c>
       <c r="F30" t="n">
-        <v>7.934049606323242</v>
+        <v>7.484410047531128</v>
       </c>
       <c r="G30" t="n">
-        <v>7.379503965377808</v>
+        <v>8.856436491012573</v>
       </c>
       <c r="H30" t="n">
-        <v>7.579389572143555</v>
+        <v>7.834025621414185</v>
       </c>
       <c r="I30" t="n">
-        <v>7.725351810455322</v>
+        <v>7.883422374725342</v>
       </c>
       <c r="J30" t="n">
-        <v>6.922940969467163</v>
+        <v>8.090923309326172</v>
       </c>
       <c r="K30" t="n">
-        <v>6.845533847808838</v>
+        <v>7.761688947677612</v>
       </c>
       <c r="L30" t="n">
-        <v>7.345655965805054</v>
+        <v>7.934429836273194</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.958055019378662</v>
+        <v>7.673507928848267</v>
       </c>
       <c r="C31" t="n">
-        <v>7.412680387496948</v>
+        <v>8.077291250228882</v>
       </c>
       <c r="D31" t="n">
-        <v>7.183391094207764</v>
+        <v>8.630476236343384</v>
       </c>
       <c r="E31" t="n">
-        <v>7.448582410812378</v>
+        <v>8.643520832061768</v>
       </c>
       <c r="F31" t="n">
-        <v>8.923810482025146</v>
+        <v>7.736971139907837</v>
       </c>
       <c r="G31" t="n">
-        <v>6.958647489547729</v>
+        <v>8.325837850570679</v>
       </c>
       <c r="H31" t="n">
-        <v>7.202967405319214</v>
+        <v>7.45459508895874</v>
       </c>
       <c r="I31" t="n">
-        <v>9.030096769332886</v>
+        <v>8.590629577636719</v>
       </c>
       <c r="J31" t="n">
-        <v>7.043212890625</v>
+        <v>7.596220254898071</v>
       </c>
       <c r="K31" t="n">
-        <v>6.976751565933228</v>
+        <v>8.174257040023804</v>
       </c>
       <c r="L31" t="n">
-        <v>7.713819551467895</v>
+        <v>8.090330719947815</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.717773914337158</v>
+        <v>8.145801305770874</v>
       </c>
       <c r="C32" t="n">
-        <v>7.659607172012329</v>
+        <v>8.993098258972168</v>
       </c>
       <c r="D32" t="n">
-        <v>11.35477614402771</v>
+        <v>8.984617710113525</v>
       </c>
       <c r="E32" t="n">
-        <v>9.493695497512817</v>
+        <v>9.225967168807983</v>
       </c>
       <c r="F32" t="n">
-        <v>8.241491079330444</v>
+        <v>8.858939409255981</v>
       </c>
       <c r="G32" t="n">
-        <v>8.382376432418823</v>
+        <v>9.039657592773438</v>
       </c>
       <c r="H32" t="n">
-        <v>8.808830738067627</v>
+        <v>8.443482160568237</v>
       </c>
       <c r="I32" t="n">
-        <v>8.398166418075562</v>
+        <v>11.35950589179993</v>
       </c>
       <c r="J32" t="n">
-        <v>10.20493316650391</v>
+        <v>8.643994331359863</v>
       </c>
       <c r="K32" t="n">
-        <v>9.669770240783691</v>
+        <v>8.640120029449463</v>
       </c>
       <c r="L32" t="n">
-        <v>9.093142080307008</v>
+        <v>9.033518385887145</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.473940134048462</v>
+        <v>8.337234735488892</v>
       </c>
       <c r="C33" t="n">
-        <v>7.746317148208618</v>
+        <v>8.121817588806152</v>
       </c>
       <c r="D33" t="n">
-        <v>7.182125568389893</v>
+        <v>7.454993486404419</v>
       </c>
       <c r="E33" t="n">
-        <v>6.768805265426636</v>
+        <v>8.352715492248535</v>
       </c>
       <c r="F33" t="n">
-        <v>8.351532459259033</v>
+        <v>8.918729305267334</v>
       </c>
       <c r="G33" t="n">
-        <v>7.356719970703125</v>
+        <v>8.144741535186768</v>
       </c>
       <c r="H33" t="n">
-        <v>7.385064601898193</v>
+        <v>9.225489854812622</v>
       </c>
       <c r="I33" t="n">
-        <v>7.723531723022461</v>
+        <v>7.596621990203857</v>
       </c>
       <c r="J33" t="n">
-        <v>8.094248294830322</v>
+        <v>7.420088529586792</v>
       </c>
       <c r="K33" t="n">
-        <v>6.994553804397583</v>
+        <v>7.358757734298706</v>
       </c>
       <c r="L33" t="n">
-        <v>7.507683897018433</v>
+        <v>8.093119025230408</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.368090629577637</v>
+        <v>7.83303165435791</v>
       </c>
       <c r="C34" t="n">
-        <v>7.913422107696533</v>
+        <v>8.03703784942627</v>
       </c>
       <c r="D34" t="n">
-        <v>8.026352882385254</v>
+        <v>8.187590360641479</v>
       </c>
       <c r="E34" t="n">
-        <v>7.567425012588501</v>
+        <v>8.365410804748535</v>
       </c>
       <c r="F34" t="n">
-        <v>7.560294628143311</v>
+        <v>7.995683193206787</v>
       </c>
       <c r="G34" t="n">
-        <v>7.867432832717896</v>
+        <v>7.876898765563965</v>
       </c>
       <c r="H34" t="n">
-        <v>7.550954580307007</v>
+        <v>8.846522092819214</v>
       </c>
       <c r="I34" t="n">
-        <v>9.538583040237427</v>
+        <v>8.171167373657227</v>
       </c>
       <c r="J34" t="n">
-        <v>9.190337181091309</v>
+        <v>8.679375410079956</v>
       </c>
       <c r="K34" t="n">
-        <v>7.352055788040161</v>
+        <v>9.151163101196289</v>
       </c>
       <c r="L34" t="n">
-        <v>7.993494868278503</v>
+        <v>8.314388060569764</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.710329294204712</v>
+        <v>9.796047925949097</v>
       </c>
       <c r="C35" t="n">
-        <v>8.34408712387085</v>
+        <v>9.118232011795044</v>
       </c>
       <c r="D35" t="n">
-        <v>8.223607540130615</v>
+        <v>8.23001766204834</v>
       </c>
       <c r="E35" t="n">
-        <v>7.469766855239868</v>
+        <v>7.799412250518799</v>
       </c>
       <c r="F35" t="n">
-        <v>7.736001253128052</v>
+        <v>8.422614097595215</v>
       </c>
       <c r="G35" t="n">
-        <v>9.520399332046509</v>
+        <v>9.011123418807983</v>
       </c>
       <c r="H35" t="n">
-        <v>7.463811159133911</v>
+        <v>8.246968269348145</v>
       </c>
       <c r="I35" t="n">
-        <v>7.292015790939331</v>
+        <v>8.069448471069336</v>
       </c>
       <c r="J35" t="n">
-        <v>9.170385360717773</v>
+        <v>8.671587228775024</v>
       </c>
       <c r="K35" t="n">
-        <v>8.252720355987549</v>
+        <v>8.742725610733032</v>
       </c>
       <c r="L35" t="n">
-        <v>8.118312406539918</v>
+        <v>8.610817694664002</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>7.384416341781616</v>
+        <v>7.745905876159668</v>
       </c>
       <c r="C36" t="n">
-        <v>7.398139715194702</v>
+        <v>9.956570863723755</v>
       </c>
       <c r="D36" t="n">
-        <v>7.476507902145386</v>
+        <v>7.517940759658813</v>
       </c>
       <c r="E36" t="n">
-        <v>8.434287786483765</v>
+        <v>7.991188287734985</v>
       </c>
       <c r="F36" t="n">
-        <v>9.380232572555542</v>
+        <v>8.054019689559937</v>
       </c>
       <c r="G36" t="n">
-        <v>9.281832218170166</v>
+        <v>8.706841945648193</v>
       </c>
       <c r="H36" t="n">
-        <v>7.130207777023315</v>
+        <v>7.41569995880127</v>
       </c>
       <c r="I36" t="n">
-        <v>7.164423704147339</v>
+        <v>11.64665770530701</v>
       </c>
       <c r="J36" t="n">
-        <v>7.700989484786987</v>
+        <v>7.411731243133545</v>
       </c>
       <c r="K36" t="n">
-        <v>7.009174585342407</v>
+        <v>8.502340316772461</v>
       </c>
       <c r="L36" t="n">
-        <v>7.836021208763123</v>
+        <v>8.494889664649964</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>8.211228370666504</v>
+        <v>8.644506216049194</v>
       </c>
       <c r="C37" t="n">
-        <v>8.461791276931763</v>
+        <v>8.045404434204102</v>
       </c>
       <c r="D37" t="n">
-        <v>8.417634010314941</v>
+        <v>7.997131824493408</v>
       </c>
       <c r="E37" t="n">
-        <v>7.400676012039185</v>
+        <v>7.491336345672607</v>
       </c>
       <c r="F37" t="n">
-        <v>7.810052394866943</v>
+        <v>7.909388542175293</v>
       </c>
       <c r="G37" t="n">
-        <v>7.356320858001709</v>
+        <v>8.093849658966064</v>
       </c>
       <c r="H37" t="n">
-        <v>7.021296977996826</v>
+        <v>7.793125867843628</v>
       </c>
       <c r="I37" t="n">
-        <v>7.756020784378052</v>
+        <v>7.997629404067993</v>
       </c>
       <c r="J37" t="n">
-        <v>7.960878849029541</v>
+        <v>7.28743577003479</v>
       </c>
       <c r="K37" t="n">
-        <v>7.908908605575562</v>
+        <v>7.338321447372437</v>
       </c>
       <c r="L37" t="n">
-        <v>7.830480813980103</v>
+        <v>7.859812951087951</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.947967767715454</v>
+        <v>7.855957269668579</v>
       </c>
       <c r="C38" t="n">
-        <v>7.343991994857788</v>
+        <v>7.579667806625366</v>
       </c>
       <c r="D38" t="n">
-        <v>7.525902271270752</v>
+        <v>8.971674680709839</v>
       </c>
       <c r="E38" t="n">
-        <v>7.538755893707275</v>
+        <v>7.882415533065796</v>
       </c>
       <c r="F38" t="n">
-        <v>7.120297431945801</v>
+        <v>8.046475172042847</v>
       </c>
       <c r="G38" t="n">
-        <v>8.191379308700562</v>
+        <v>8.119778633117676</v>
       </c>
       <c r="H38" t="n">
-        <v>7.598117589950562</v>
+        <v>7.350223064422607</v>
       </c>
       <c r="I38" t="n">
-        <v>7.286679983139038</v>
+        <v>7.536409139633179</v>
       </c>
       <c r="J38" t="n">
-        <v>6.96846342086792</v>
+        <v>8.763673305511475</v>
       </c>
       <c r="K38" t="n">
-        <v>7.262585878372192</v>
+        <v>8.060515642166138</v>
       </c>
       <c r="L38" t="n">
-        <v>7.378414154052734</v>
+        <v>8.01667902469635</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>7.659531354904175</v>
+        <v>8.570204734802246</v>
       </c>
       <c r="C39" t="n">
-        <v>7.620537042617798</v>
+        <v>8.605190753936768</v>
       </c>
       <c r="D39" t="n">
-        <v>8.005312919616699</v>
+        <v>9.090327501296997</v>
       </c>
       <c r="E39" t="n">
-        <v>7.653472185134888</v>
+        <v>8.07338809967041</v>
       </c>
       <c r="F39" t="n">
-        <v>7.739007234573364</v>
+        <v>8.713309049606323</v>
       </c>
       <c r="G39" t="n">
-        <v>10.11915516853333</v>
+        <v>8.100815534591675</v>
       </c>
       <c r="H39" t="n">
-        <v>7.654634952545166</v>
+        <v>7.731808662414551</v>
       </c>
       <c r="I39" t="n">
-        <v>7.778365612030029</v>
+        <v>9.247426986694336</v>
       </c>
       <c r="J39" t="n">
-        <v>7.745964050292969</v>
+        <v>8.262922763824463</v>
       </c>
       <c r="K39" t="n">
-        <v>7.820642709732056</v>
+        <v>8.050476312637329</v>
       </c>
       <c r="L39" t="n">
-        <v>7.979662322998047</v>
+        <v>8.44458703994751</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.134868860244751</v>
+        <v>8.097843885421753</v>
       </c>
       <c r="C40" t="n">
-        <v>7.213011026382446</v>
+        <v>7.645541667938232</v>
       </c>
       <c r="D40" t="n">
-        <v>7.058030843734741</v>
+        <v>7.639535903930664</v>
       </c>
       <c r="E40" t="n">
-        <v>7.355550050735474</v>
+        <v>7.8709876537323</v>
       </c>
       <c r="F40" t="n">
-        <v>7.650979280471802</v>
+        <v>7.589647531509399</v>
       </c>
       <c r="G40" t="n">
-        <v>7.790619611740112</v>
+        <v>7.471982002258301</v>
       </c>
       <c r="H40" t="n">
-        <v>8.398804187774658</v>
+        <v>8.618044853210449</v>
       </c>
       <c r="I40" t="n">
-        <v>9.956385612487793</v>
+        <v>7.429051876068115</v>
       </c>
       <c r="J40" t="n">
-        <v>7.068986892700195</v>
+        <v>7.675947904586792</v>
       </c>
       <c r="K40" t="n">
-        <v>7.167280197143555</v>
+        <v>8.215124130249023</v>
       </c>
       <c r="L40" t="n">
-        <v>7.679451656341553</v>
+        <v>7.825370740890503</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>6.56394362449646</v>
+        <v>7.782174825668335</v>
       </c>
       <c r="C41" t="n">
-        <v>6.672628879547119</v>
+        <v>9.175338745117188</v>
       </c>
       <c r="D41" t="n">
-        <v>7.868048906326294</v>
+        <v>7.190274953842163</v>
       </c>
       <c r="E41" t="n">
-        <v>7.797245025634766</v>
+        <v>7.57927942276001</v>
       </c>
       <c r="F41" t="n">
-        <v>6.917493581771851</v>
+        <v>7.353363275527954</v>
       </c>
       <c r="G41" t="n">
-        <v>6.715065717697144</v>
+        <v>7.994189977645874</v>
       </c>
       <c r="H41" t="n">
-        <v>7.069118499755859</v>
+        <v>7.652080774307251</v>
       </c>
       <c r="I41" t="n">
-        <v>6.939581632614136</v>
+        <v>7.579703569412231</v>
       </c>
       <c r="J41" t="n">
-        <v>6.672504186630249</v>
+        <v>7.76069712638855</v>
       </c>
       <c r="K41" t="n">
-        <v>6.541837215423584</v>
+        <v>7.205631971359253</v>
       </c>
       <c r="L41" t="n">
-        <v>6.975746726989746</v>
+        <v>7.727273464202881</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>8.224040508270264</v>
+        <v>7.730781078338623</v>
       </c>
       <c r="C42" t="n">
-        <v>9.959650993347168</v>
+        <v>8.136955261230469</v>
       </c>
       <c r="D42" t="n">
-        <v>7.03109073638916</v>
+        <v>7.733790159225464</v>
       </c>
       <c r="E42" t="n">
-        <v>7.729827880859375</v>
+        <v>9.729661464691162</v>
       </c>
       <c r="F42" t="n">
-        <v>8.552685976028442</v>
+        <v>8.291350603103638</v>
       </c>
       <c r="G42" t="n">
-        <v>7.412112474441528</v>
+        <v>7.589140176773071</v>
       </c>
       <c r="H42" t="n">
-        <v>7.439050197601318</v>
+        <v>7.584650039672852</v>
       </c>
       <c r="I42" t="n">
-        <v>7.577705144882202</v>
+        <v>7.760696411132812</v>
       </c>
       <c r="J42" t="n">
-        <v>7.567220687866211</v>
+        <v>8.120792627334595</v>
       </c>
       <c r="K42" t="n">
-        <v>7.772627115249634</v>
+        <v>8.023066759109497</v>
       </c>
       <c r="L42" t="n">
-        <v>7.92660117149353</v>
+        <v>8.070088458061218</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.221218824386597</v>
+        <v>7.755631685256958</v>
       </c>
       <c r="C43" t="n">
-        <v>6.644715070724487</v>
+        <v>8.045112609863281</v>
       </c>
       <c r="D43" t="n">
-        <v>7.759823322296143</v>
+        <v>8.005208730697632</v>
       </c>
       <c r="E43" t="n">
-        <v>7.489514350891113</v>
+        <v>8.322861671447754</v>
       </c>
       <c r="F43" t="n">
-        <v>6.803319931030273</v>
+        <v>7.912909507751465</v>
       </c>
       <c r="G43" t="n">
-        <v>8.761194467544556</v>
+        <v>7.538857698440552</v>
       </c>
       <c r="H43" t="n">
-        <v>7.482555389404297</v>
+        <v>7.837087869644165</v>
       </c>
       <c r="I43" t="n">
-        <v>7.322487592697144</v>
+        <v>9.553872346878052</v>
       </c>
       <c r="J43" t="n">
-        <v>7.242675542831421</v>
+        <v>13.22472476959229</v>
       </c>
       <c r="K43" t="n">
-        <v>6.953409194946289</v>
+        <v>7.309037208557129</v>
       </c>
       <c r="L43" t="n">
-        <v>7.368091368675232</v>
+        <v>8.550530409812927</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.272197246551514</v>
+        <v>7.269702672958374</v>
       </c>
       <c r="C44" t="n">
-        <v>6.025342702865601</v>
+        <v>7.123962640762329</v>
       </c>
       <c r="D44" t="n">
-        <v>7.029756784439087</v>
+        <v>6.751917600631714</v>
       </c>
       <c r="E44" t="n">
-        <v>6.570928812026978</v>
+        <v>6.932475566864014</v>
       </c>
       <c r="F44" t="n">
-        <v>6.639608383178711</v>
+        <v>6.706035137176514</v>
       </c>
       <c r="G44" t="n">
-        <v>6.67203164100647</v>
+        <v>7.145363569259644</v>
       </c>
       <c r="H44" t="n">
-        <v>6.812641143798828</v>
+        <v>6.706409692764282</v>
       </c>
       <c r="I44" t="n">
-        <v>6.707415580749512</v>
+        <v>8.141188144683838</v>
       </c>
       <c r="J44" t="n">
-        <v>7.01113224029541</v>
+        <v>6.813112258911133</v>
       </c>
       <c r="K44" t="n">
-        <v>6.838564395904541</v>
+        <v>6.922358989715576</v>
       </c>
       <c r="L44" t="n">
-        <v>6.657961893081665</v>
+        <v>7.051252627372742</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.12378716468811</v>
+        <v>10.03043246269226</v>
       </c>
       <c r="C45" t="n">
-        <v>9.186557531356812</v>
+        <v>8.669883728027344</v>
       </c>
       <c r="D45" t="n">
-        <v>8.284376621246338</v>
+        <v>8.342736482620239</v>
       </c>
       <c r="E45" t="n">
-        <v>9.353724002838135</v>
+        <v>9.028999328613281</v>
       </c>
       <c r="F45" t="n">
-        <v>8.536996603012085</v>
+        <v>10.39399719238281</v>
       </c>
       <c r="G45" t="n">
-        <v>7.698445796966553</v>
+        <v>9.635428428649902</v>
       </c>
       <c r="H45" t="n">
-        <v>8.603628158569336</v>
+        <v>9.310770750045776</v>
       </c>
       <c r="I45" t="n">
-        <v>8.551254987716675</v>
+        <v>9.763114929199219</v>
       </c>
       <c r="J45" t="n">
-        <v>9.440434455871582</v>
+        <v>9.753620386123657</v>
       </c>
       <c r="K45" t="n">
-        <v>8.601630687713623</v>
+        <v>8.798567533493042</v>
       </c>
       <c r="L45" t="n">
-        <v>8.638083600997925</v>
+        <v>9.372755122184753</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.794743061065674</v>
+        <v>7.828064203262329</v>
       </c>
       <c r="C46" t="n">
-        <v>7.150906324386597</v>
+        <v>7.81807279586792</v>
       </c>
       <c r="D46" t="n">
-        <v>9.120804309844971</v>
+        <v>6.876971960067749</v>
       </c>
       <c r="E46" t="n">
-        <v>7.987246036529541</v>
+        <v>8.04748797416687</v>
       </c>
       <c r="F46" t="n">
-        <v>7.676523685455322</v>
+        <v>8.173183679580688</v>
       </c>
       <c r="G46" t="n">
-        <v>6.890059232711792</v>
+        <v>7.604110240936279</v>
       </c>
       <c r="H46" t="n">
-        <v>7.391762018203735</v>
+        <v>7.177732467651367</v>
       </c>
       <c r="I46" t="n">
-        <v>9.464424133300781</v>
+        <v>10.14361834526062</v>
       </c>
       <c r="J46" t="n">
-        <v>8.631073951721191</v>
+        <v>7.345301389694214</v>
       </c>
       <c r="K46" t="n">
-        <v>6.695569515228271</v>
+        <v>7.852024555206299</v>
       </c>
       <c r="L46" t="n">
-        <v>7.880311226844787</v>
+        <v>7.886656761169434</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.972680568695068</v>
+        <v>9.305825471878052</v>
       </c>
       <c r="C47" t="n">
-        <v>8.316911220550537</v>
+        <v>8.097857475280762</v>
       </c>
       <c r="D47" t="n">
-        <v>7.61620569229126</v>
+        <v>9.339727163314819</v>
       </c>
       <c r="E47" t="n">
-        <v>7.381824731826782</v>
+        <v>8.691335678100586</v>
       </c>
       <c r="F47" t="n">
-        <v>8.115385293960571</v>
+        <v>8.144711017608643</v>
       </c>
       <c r="G47" t="n">
-        <v>8.691416263580322</v>
+        <v>9.97310996055603</v>
       </c>
       <c r="H47" t="n">
-        <v>7.677548885345459</v>
+        <v>8.991090059280396</v>
       </c>
       <c r="I47" t="n">
-        <v>7.927890777587891</v>
+        <v>8.223036527633667</v>
       </c>
       <c r="J47" t="n">
-        <v>9.817852973937988</v>
+        <v>8.545743227005005</v>
       </c>
       <c r="K47" t="n">
-        <v>8.251011848449707</v>
+        <v>12.08879113197327</v>
       </c>
       <c r="L47" t="n">
-        <v>8.276872825622558</v>
+        <v>9.140122771263123</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.230124711990356</v>
+        <v>7.065612316131592</v>
       </c>
       <c r="C48" t="n">
-        <v>6.639600992202759</v>
+        <v>6.815279483795166</v>
       </c>
       <c r="D48" t="n">
-        <v>6.568786144256592</v>
+        <v>6.972844123840332</v>
       </c>
       <c r="E48" t="n">
-        <v>6.600207328796387</v>
+        <v>7.184303283691406</v>
       </c>
       <c r="F48" t="n">
-        <v>6.887962818145752</v>
+        <v>7.300504446029663</v>
       </c>
       <c r="G48" t="n">
-        <v>7.651518106460571</v>
+        <v>7.186784029006958</v>
       </c>
       <c r="H48" t="n">
-        <v>6.734343290328979</v>
+        <v>7.702445507049561</v>
       </c>
       <c r="I48" t="n">
-        <v>6.919857740402222</v>
+        <v>8.38916015625</v>
       </c>
       <c r="J48" t="n">
-        <v>7.974666595458984</v>
+        <v>7.022696733474731</v>
       </c>
       <c r="K48" t="n">
-        <v>6.534829378128052</v>
+        <v>6.915495157241821</v>
       </c>
       <c r="L48" t="n">
-        <v>6.874189710617065</v>
+        <v>7.255512523651123</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>6.69049072265625</v>
+        <v>7.81694483757019</v>
       </c>
       <c r="C49" t="n">
-        <v>7.01213550567627</v>
+        <v>7.473452806472778</v>
       </c>
       <c r="D49" t="n">
-        <v>8.200101852416992</v>
+        <v>7.736948251724243</v>
       </c>
       <c r="E49" t="n">
-        <v>7.426066637039185</v>
+        <v>7.491393804550171</v>
       </c>
       <c r="F49" t="n">
-        <v>6.777230262756348</v>
+        <v>7.913834571838379</v>
       </c>
       <c r="G49" t="n">
-        <v>6.904911279678345</v>
+        <v>7.297323226928711</v>
       </c>
       <c r="H49" t="n">
-        <v>7.045575857162476</v>
+        <v>8.625551462173462</v>
       </c>
       <c r="I49" t="n">
-        <v>7.306374788284302</v>
+        <v>7.731408596038818</v>
       </c>
       <c r="J49" t="n">
-        <v>6.756775856018066</v>
+        <v>7.773775339126587</v>
       </c>
       <c r="K49" t="n">
-        <v>7.108383178710938</v>
+        <v>7.489997148513794</v>
       </c>
       <c r="L49" t="n">
-        <v>7.122804594039917</v>
+        <v>7.735063004493713</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>8.123815298080444</v>
+        <v>10.22341251373291</v>
       </c>
       <c r="C50" t="n">
-        <v>9.456927537918091</v>
+        <v>8.09044623374939</v>
       </c>
       <c r="D50" t="n">
-        <v>9.352152585983276</v>
+        <v>8.638487100601196</v>
       </c>
       <c r="E50" t="n">
-        <v>8.071412324905396</v>
+        <v>9.548659324645996</v>
       </c>
       <c r="F50" t="n">
-        <v>7.541295051574707</v>
+        <v>8.215624094009399</v>
       </c>
       <c r="G50" t="n">
-        <v>7.745590209960938</v>
+        <v>8.390157461166382</v>
       </c>
       <c r="H50" t="n">
-        <v>6.924461841583252</v>
+        <v>8.649712324142456</v>
       </c>
       <c r="I50" t="n">
-        <v>8.325843095779419</v>
+        <v>9.100932598114014</v>
       </c>
       <c r="J50" t="n">
-        <v>7.575796127319336</v>
+        <v>7.417107105255127</v>
       </c>
       <c r="K50" t="n">
-        <v>7.347911596298218</v>
+        <v>10.71816897392273</v>
       </c>
       <c r="L50" t="n">
-        <v>8.046520566940307</v>
+        <v>8.89927077293396</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.410318613052368</v>
+        <v>7.30685019493103</v>
       </c>
       <c r="C51" t="n">
-        <v>6.664657115936279</v>
+        <v>9.451913595199585</v>
       </c>
       <c r="D51" t="n">
-        <v>7.166361570358276</v>
+        <v>7.511314153671265</v>
       </c>
       <c r="E51" t="n">
-        <v>6.666640043258667</v>
+        <v>8.921738624572754</v>
       </c>
       <c r="F51" t="n">
-        <v>6.547481298446655</v>
+        <v>7.836033344268799</v>
       </c>
       <c r="G51" t="n">
-        <v>6.825741291046143</v>
+        <v>7.883376359939575</v>
       </c>
       <c r="H51" t="n">
-        <v>6.533517599105835</v>
+        <v>7.202624797821045</v>
       </c>
       <c r="I51" t="n">
-        <v>7.018763780593872</v>
+        <v>7.229549169540405</v>
       </c>
       <c r="J51" t="n">
-        <v>7.300501108169556</v>
+        <v>8.060431003570557</v>
       </c>
       <c r="K51" t="n">
-        <v>6.468167066574097</v>
+        <v>7.275135040283203</v>
       </c>
       <c r="L51" t="n">
-        <v>6.760214948654175</v>
+        <v>7.867896628379822</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.721541924476623</v>
+        <v>8.216508088111878</v>
       </c>
       <c r="C52" t="n">
-        <v>7.625573930740356</v>
+        <v>8.138205828666687</v>
       </c>
       <c r="D52" t="n">
-        <v>7.865109462738037</v>
+        <v>8.213507437705994</v>
       </c>
       <c r="E52" t="n">
-        <v>7.758266901969909</v>
+        <v>8.218374695777893</v>
       </c>
       <c r="F52" t="n">
-        <v>7.740560903549194</v>
+        <v>8.137386541366578</v>
       </c>
       <c r="G52" t="n">
-        <v>7.735372104644775</v>
+        <v>8.206611423492431</v>
       </c>
       <c r="H52" t="n">
-        <v>7.616848721504211</v>
+        <v>8.035492215156555</v>
       </c>
       <c r="I52" t="n">
-        <v>7.919887962341309</v>
+        <v>8.578531947135925</v>
       </c>
       <c r="J52" t="n">
-        <v>7.812759943008423</v>
+        <v>8.274374213218689</v>
       </c>
       <c r="K52" t="n">
-        <v>7.547772111892701</v>
+        <v>8.19133270263672</v>
       </c>
       <c r="L52" t="n">
-        <v>7.734369396686555</v>
+        <v>8.221032509326934</v>
       </c>
     </row>
   </sheetData>
